--- a/Nadlan/nadlan.xlsx
+++ b/Nadlan/nadlan.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saarp\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saarp\Documents\GitHub\portfolio\Nadlan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D8EABA-474A-420F-B1CA-97963A8F540A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588B2310-64CB-4228-9248-0872F2032310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Real Estate Transactions" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="97">
   <si>
     <t>year</t>
   </si>
@@ -321,6 +326,12 @@
   </si>
   <si>
     <t>ous</t>
+  </si>
+  <si>
+    <t>2025-4</t>
+  </si>
+  <si>
+    <t>2025-Q2</t>
   </si>
 </sst>
 </file>
@@ -393,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -409,6 +420,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,6 +438,1913 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="לוח 1 table"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="13">
+          <cell r="B13">
+            <v>4239</v>
+          </cell>
+          <cell r="C13">
+            <v>4229</v>
+          </cell>
+          <cell r="D13">
+            <v>4600</v>
+          </cell>
+          <cell r="G13">
+            <v>2384</v>
+          </cell>
+          <cell r="H13">
+            <v>2150</v>
+          </cell>
+          <cell r="I13">
+            <v>2500</v>
+          </cell>
+          <cell r="K13">
+            <v>6679</v>
+          </cell>
+          <cell r="L13">
+            <v>6378</v>
+          </cell>
+          <cell r="M13">
+            <v>7100</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>4078</v>
+          </cell>
+          <cell r="C14">
+            <v>3969</v>
+          </cell>
+          <cell r="D14">
+            <v>3895</v>
+          </cell>
+          <cell r="G14">
+            <v>2337</v>
+          </cell>
+          <cell r="H14">
+            <v>2561</v>
+          </cell>
+          <cell r="I14">
+            <v>2441</v>
+          </cell>
+          <cell r="K14">
+            <v>6450</v>
+          </cell>
+          <cell r="L14">
+            <v>6530</v>
+          </cell>
+          <cell r="M14">
+            <v>6336</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>3936</v>
+          </cell>
+          <cell r="C15">
+            <v>3967</v>
+          </cell>
+          <cell r="D15">
+            <v>4496</v>
+          </cell>
+          <cell r="G15">
+            <v>2321</v>
+          </cell>
+          <cell r="H15">
+            <v>2303</v>
+          </cell>
+          <cell r="I15">
+            <v>2727</v>
+          </cell>
+          <cell r="K15">
+            <v>6275</v>
+          </cell>
+          <cell r="L15">
+            <v>6270</v>
+          </cell>
+          <cell r="M15">
+            <v>7223</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>3811</v>
+          </cell>
+          <cell r="C16">
+            <v>3775</v>
+          </cell>
+          <cell r="D16">
+            <v>2695</v>
+          </cell>
+          <cell r="G16">
+            <v>2338</v>
+          </cell>
+          <cell r="H16">
+            <v>2323</v>
+          </cell>
+          <cell r="I16">
+            <v>1456</v>
+          </cell>
+          <cell r="K16">
+            <v>6172</v>
+          </cell>
+          <cell r="L16">
+            <v>6098</v>
+          </cell>
+          <cell r="M16">
+            <v>4151</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>3706</v>
+          </cell>
+          <cell r="C17">
+            <v>3738</v>
+          </cell>
+          <cell r="D17">
+            <v>3994</v>
+          </cell>
+          <cell r="G17">
+            <v>2383</v>
+          </cell>
+          <cell r="H17">
+            <v>2380</v>
+          </cell>
+          <cell r="I17">
+            <v>2225</v>
+          </cell>
+          <cell r="K17">
+            <v>6158</v>
+          </cell>
+          <cell r="L17">
+            <v>6118</v>
+          </cell>
+          <cell r="M17">
+            <v>6219</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>3627</v>
+          </cell>
+          <cell r="C18">
+            <v>3761</v>
+          </cell>
+          <cell r="D18">
+            <v>4223</v>
+          </cell>
+          <cell r="G18">
+            <v>2452</v>
+          </cell>
+          <cell r="H18">
+            <v>2453</v>
+          </cell>
+          <cell r="I18">
+            <v>2829</v>
+          </cell>
+          <cell r="K18">
+            <v>6240</v>
+          </cell>
+          <cell r="L18">
+            <v>6215</v>
+          </cell>
+          <cell r="M18">
+            <v>7052</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>3580</v>
+          </cell>
+          <cell r="C19">
+            <v>3593</v>
+          </cell>
+          <cell r="D19">
+            <v>4055</v>
+          </cell>
+          <cell r="G19">
+            <v>2537</v>
+          </cell>
+          <cell r="H19">
+            <v>2450</v>
+          </cell>
+          <cell r="I19">
+            <v>2503</v>
+          </cell>
+          <cell r="K19">
+            <v>6410</v>
+          </cell>
+          <cell r="L19">
+            <v>6043</v>
+          </cell>
+          <cell r="M19">
+            <v>6558</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>3573</v>
+          </cell>
+          <cell r="C20">
+            <v>4103</v>
+          </cell>
+          <cell r="D20">
+            <v>4345</v>
+          </cell>
+          <cell r="G20">
+            <v>2634</v>
+          </cell>
+          <cell r="H20">
+            <v>3109</v>
+          </cell>
+          <cell r="I20">
+            <v>3201</v>
+          </cell>
+          <cell r="K20">
+            <v>6649</v>
+          </cell>
+          <cell r="L20">
+            <v>7211</v>
+          </cell>
+          <cell r="M20">
+            <v>7546</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>3611</v>
+          </cell>
+          <cell r="C21">
+            <v>3634</v>
+          </cell>
+          <cell r="D21">
+            <v>3468</v>
+          </cell>
+          <cell r="G21">
+            <v>2745</v>
+          </cell>
+          <cell r="H21">
+            <v>2869</v>
+          </cell>
+          <cell r="I21">
+            <v>2389</v>
+          </cell>
+          <cell r="K21">
+            <v>6926</v>
+          </cell>
+          <cell r="L21">
+            <v>6502</v>
+          </cell>
+          <cell r="M21">
+            <v>5857</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>3700</v>
+          </cell>
+          <cell r="C22">
+            <v>2373</v>
+          </cell>
+          <cell r="D22">
+            <v>1636</v>
+          </cell>
+          <cell r="G22">
+            <v>2879</v>
+          </cell>
+          <cell r="H22">
+            <v>1035</v>
+          </cell>
+          <cell r="I22">
+            <v>867</v>
+          </cell>
+          <cell r="K22">
+            <v>7212</v>
+          </cell>
+          <cell r="L22">
+            <v>3408</v>
+          </cell>
+          <cell r="M22">
+            <v>2503</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>3835</v>
+          </cell>
+          <cell r="C23">
+            <v>2893</v>
+          </cell>
+          <cell r="D23">
+            <v>2982</v>
+          </cell>
+          <cell r="G23">
+            <v>3044</v>
+          </cell>
+          <cell r="H23">
+            <v>1506</v>
+          </cell>
+          <cell r="I23">
+            <v>1553</v>
+          </cell>
+          <cell r="K23">
+            <v>7491</v>
+          </cell>
+          <cell r="L23">
+            <v>4400</v>
+          </cell>
+          <cell r="M23">
+            <v>4535</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>4005</v>
+          </cell>
+          <cell r="C24">
+            <v>3806</v>
+          </cell>
+          <cell r="D24">
+            <v>3707</v>
+          </cell>
+          <cell r="G24">
+            <v>3236</v>
+          </cell>
+          <cell r="H24">
+            <v>2524</v>
+          </cell>
+          <cell r="I24">
+            <v>2859</v>
+          </cell>
+          <cell r="K24">
+            <v>7756</v>
+          </cell>
+          <cell r="L24">
+            <v>6331</v>
+          </cell>
+          <cell r="M24">
+            <v>6566</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>4191</v>
+          </cell>
+          <cell r="C25">
+            <v>4471</v>
+          </cell>
+          <cell r="D25">
+            <v>4825</v>
+          </cell>
+          <cell r="G25">
+            <v>3440</v>
+          </cell>
+          <cell r="H25">
+            <v>3810</v>
+          </cell>
+          <cell r="I25">
+            <v>3958</v>
+          </cell>
+          <cell r="K25">
+            <v>8005</v>
+          </cell>
+          <cell r="L25">
+            <v>8282</v>
+          </cell>
+          <cell r="M25">
+            <v>8783</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>4377</v>
+          </cell>
+          <cell r="C26">
+            <v>4518</v>
+          </cell>
+          <cell r="D26">
+            <v>4600</v>
+          </cell>
+          <cell r="G26">
+            <v>3627</v>
+          </cell>
+          <cell r="H26">
+            <v>3684</v>
+          </cell>
+          <cell r="I26">
+            <v>3795</v>
+          </cell>
+          <cell r="K26">
+            <v>8239</v>
+          </cell>
+          <cell r="L26">
+            <v>8202</v>
+          </cell>
+          <cell r="M26">
+            <v>8395</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>4550</v>
+          </cell>
+          <cell r="C27">
+            <v>4614</v>
+          </cell>
+          <cell r="D27">
+            <v>4794</v>
+          </cell>
+          <cell r="G27">
+            <v>3775</v>
+          </cell>
+          <cell r="H27">
+            <v>3826</v>
+          </cell>
+          <cell r="I27">
+            <v>3957</v>
+          </cell>
+          <cell r="K27">
+            <v>8447</v>
+          </cell>
+          <cell r="L27">
+            <v>8440</v>
+          </cell>
+          <cell r="M27">
+            <v>8751</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>4705</v>
+          </cell>
+          <cell r="C28">
+            <v>4686</v>
+          </cell>
+          <cell r="D28">
+            <v>4328</v>
+          </cell>
+          <cell r="G28">
+            <v>3866</v>
+          </cell>
+          <cell r="H28">
+            <v>3916</v>
+          </cell>
+          <cell r="I28">
+            <v>3505</v>
+          </cell>
+          <cell r="K28">
+            <v>8608</v>
+          </cell>
+          <cell r="L28">
+            <v>8602</v>
+          </cell>
+          <cell r="M28">
+            <v>7833</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>4844</v>
+          </cell>
+          <cell r="C29">
+            <v>4614</v>
+          </cell>
+          <cell r="D29">
+            <v>4549</v>
+          </cell>
+          <cell r="G29">
+            <v>3893</v>
+          </cell>
+          <cell r="H29">
+            <v>3860</v>
+          </cell>
+          <cell r="I29">
+            <v>3923</v>
+          </cell>
+          <cell r="K29">
+            <v>8697</v>
+          </cell>
+          <cell r="L29">
+            <v>8475</v>
+          </cell>
+          <cell r="M29">
+            <v>8472</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>4978</v>
+          </cell>
+          <cell r="C30">
+            <v>4978</v>
+          </cell>
+          <cell r="D30">
+            <v>5023</v>
+          </cell>
+          <cell r="G30">
+            <v>3862</v>
+          </cell>
+          <cell r="H30">
+            <v>3859</v>
+          </cell>
+          <cell r="I30">
+            <v>3787</v>
+          </cell>
+          <cell r="K30">
+            <v>8696</v>
+          </cell>
+          <cell r="L30">
+            <v>8838</v>
+          </cell>
+          <cell r="M30">
+            <v>8810</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>5109</v>
+          </cell>
+          <cell r="C31">
+            <v>5088</v>
+          </cell>
+          <cell r="D31">
+            <v>5676</v>
+          </cell>
+          <cell r="G31">
+            <v>3789</v>
+          </cell>
+          <cell r="H31">
+            <v>4043</v>
+          </cell>
+          <cell r="I31">
+            <v>4024</v>
+          </cell>
+          <cell r="K31">
+            <v>8608</v>
+          </cell>
+          <cell r="L31">
+            <v>9131</v>
+          </cell>
+          <cell r="M31">
+            <v>9700</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>5232</v>
+          </cell>
+          <cell r="C32">
+            <v>5176</v>
+          </cell>
+          <cell r="D32">
+            <v>4496</v>
+          </cell>
+          <cell r="G32">
+            <v>3689</v>
+          </cell>
+          <cell r="H32">
+            <v>3726</v>
+          </cell>
+          <cell r="I32">
+            <v>3487</v>
+          </cell>
+          <cell r="K32">
+            <v>8455</v>
+          </cell>
+          <cell r="L32">
+            <v>8902</v>
+          </cell>
+          <cell r="M32">
+            <v>7983</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33">
+            <v>5332</v>
+          </cell>
+          <cell r="C33">
+            <v>5130</v>
+          </cell>
+          <cell r="D33">
+            <v>5264</v>
+          </cell>
+          <cell r="G33">
+            <v>3579</v>
+          </cell>
+          <cell r="H33">
+            <v>3467</v>
+          </cell>
+          <cell r="I33">
+            <v>3736</v>
+          </cell>
+          <cell r="K33">
+            <v>8283</v>
+          </cell>
+          <cell r="L33">
+            <v>8597</v>
+          </cell>
+          <cell r="M33">
+            <v>9000</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34">
+            <v>5385</v>
+          </cell>
+          <cell r="C34">
+            <v>3952</v>
+          </cell>
+          <cell r="D34">
+            <v>3194</v>
+          </cell>
+          <cell r="G34">
+            <v>3467</v>
+          </cell>
+          <cell r="H34">
+            <v>3455</v>
+          </cell>
+          <cell r="I34">
+            <v>2400</v>
+          </cell>
+          <cell r="K34">
+            <v>8129</v>
+          </cell>
+          <cell r="L34">
+            <v>7408</v>
+          </cell>
+          <cell r="M34">
+            <v>5594</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35">
+            <v>5375</v>
+          </cell>
+          <cell r="C35">
+            <v>4231</v>
+          </cell>
+          <cell r="D35">
+            <v>4414</v>
+          </cell>
+          <cell r="G35">
+            <v>3356</v>
+          </cell>
+          <cell r="H35">
+            <v>3041</v>
+          </cell>
+          <cell r="I35">
+            <v>3130</v>
+          </cell>
+          <cell r="K35">
+            <v>8012</v>
+          </cell>
+          <cell r="L35">
+            <v>7272</v>
+          </cell>
+          <cell r="M35">
+            <v>7544</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36">
+            <v>5297</v>
+          </cell>
+          <cell r="C36">
+            <v>5438</v>
+          </cell>
+          <cell r="D36">
+            <v>5782</v>
+          </cell>
+          <cell r="G36">
+            <v>3248</v>
+          </cell>
+          <cell r="H36">
+            <v>4995</v>
+          </cell>
+          <cell r="I36">
+            <v>6518</v>
+          </cell>
+          <cell r="K36">
+            <v>7928</v>
+          </cell>
+          <cell r="L36">
+            <v>10432</v>
+          </cell>
+          <cell r="M36">
+            <v>12300</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37">
+            <v>5164</v>
+          </cell>
+          <cell r="C37">
+            <v>5186</v>
+          </cell>
+          <cell r="D37">
+            <v>5074</v>
+          </cell>
+          <cell r="G37">
+            <v>3145</v>
+          </cell>
+          <cell r="H37">
+            <v>3307</v>
+          </cell>
+          <cell r="I37">
+            <v>3192</v>
+          </cell>
+          <cell r="K37">
+            <v>7856</v>
+          </cell>
+          <cell r="L37">
+            <v>8492</v>
+          </cell>
+          <cell r="M37">
+            <v>8266</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38">
+            <v>4997</v>
+          </cell>
+          <cell r="C38">
+            <v>4873</v>
+          </cell>
+          <cell r="D38">
+            <v>4794</v>
+          </cell>
+          <cell r="G38">
+            <v>3044</v>
+          </cell>
+          <cell r="H38">
+            <v>3124</v>
+          </cell>
+          <cell r="I38">
+            <v>3025</v>
+          </cell>
+          <cell r="K38">
+            <v>7769</v>
+          </cell>
+          <cell r="L38">
+            <v>7997</v>
+          </cell>
+          <cell r="M38">
+            <v>7819</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39">
+            <v>4826</v>
+          </cell>
+          <cell r="C39">
+            <v>4627</v>
+          </cell>
+          <cell r="D39">
+            <v>5112</v>
+          </cell>
+          <cell r="G39">
+            <v>2948</v>
+          </cell>
+          <cell r="H39">
+            <v>2912</v>
+          </cell>
+          <cell r="I39">
+            <v>3216</v>
+          </cell>
+          <cell r="K39">
+            <v>7656</v>
+          </cell>
+          <cell r="L39">
+            <v>7539</v>
+          </cell>
+          <cell r="M39">
+            <v>8328</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40">
+            <v>4681</v>
+          </cell>
+          <cell r="C40">
+            <v>4507</v>
+          </cell>
+          <cell r="D40">
+            <v>3929</v>
+          </cell>
+          <cell r="G40">
+            <v>2865</v>
+          </cell>
+          <cell r="H40">
+            <v>2734</v>
+          </cell>
+          <cell r="I40">
+            <v>2353</v>
+          </cell>
+          <cell r="K40">
+            <v>7521</v>
+          </cell>
+          <cell r="L40">
+            <v>7242</v>
+          </cell>
+          <cell r="M40">
+            <v>6282</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="9">
+          <cell r="C9">
+            <v>52324</v>
+          </cell>
+          <cell r="D9">
+            <v>52606</v>
+          </cell>
+          <cell r="E9">
+            <v>54118</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>53345</v>
+          </cell>
+          <cell r="D10">
+            <v>55306</v>
+          </cell>
+          <cell r="E10">
+            <v>54457</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>54382</v>
+          </cell>
+          <cell r="D11">
+            <v>53978</v>
+          </cell>
+          <cell r="E11">
+            <v>54096</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>55435</v>
+          </cell>
+          <cell r="D12">
+            <v>55493</v>
+          </cell>
+          <cell r="E12">
+            <v>55672</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>56518</v>
+          </cell>
+          <cell r="D13">
+            <v>56838</v>
+          </cell>
+          <cell r="E13">
+            <v>56899</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>57647</v>
+          </cell>
+          <cell r="D14">
+            <v>57609</v>
+          </cell>
+          <cell r="E14">
+            <v>57098</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>58832</v>
+          </cell>
+          <cell r="D15">
+            <v>58719</v>
+          </cell>
+          <cell r="E15">
+            <v>58404</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>60067</v>
+          </cell>
+          <cell r="D16">
+            <v>59117</v>
+          </cell>
+          <cell r="E16">
+            <v>58705</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>61324</v>
+          </cell>
+          <cell r="D17">
+            <v>61739</v>
+          </cell>
+          <cell r="E17">
+            <v>61068</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>62560</v>
+          </cell>
+          <cell r="D18">
+            <v>62671</v>
+          </cell>
+          <cell r="E18">
+            <v>61581</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>63724</v>
+          </cell>
+          <cell r="D19">
+            <v>63678</v>
+          </cell>
+          <cell r="E19">
+            <v>64002</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>64763</v>
+          </cell>
+          <cell r="D20">
+            <v>67512</v>
+          </cell>
+          <cell r="E20">
+            <v>68995</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>65649</v>
+          </cell>
+          <cell r="D21">
+            <v>66161</v>
+          </cell>
+          <cell r="E21">
+            <v>68632</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>66380</v>
+          </cell>
+          <cell r="D22">
+            <v>66074</v>
+          </cell>
+          <cell r="E22">
+            <v>67910</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>66971</v>
+          </cell>
+          <cell r="D23">
+            <v>67490</v>
+          </cell>
+          <cell r="E23">
+            <v>67015</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>67452</v>
+          </cell>
+          <cell r="D24">
+            <v>67448</v>
+          </cell>
+          <cell r="E24">
+            <v>65876</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>67869</v>
+          </cell>
+          <cell r="D25">
+            <v>67768</v>
+          </cell>
+          <cell r="E25">
+            <v>66841</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>68270</v>
+          </cell>
+          <cell r="D26">
+            <v>68610</v>
+          </cell>
+          <cell r="E26">
+            <v>67619</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>68722</v>
+          </cell>
+          <cell r="D27">
+            <v>69033</v>
+          </cell>
+          <cell r="E27">
+            <v>68877</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>69302</v>
+          </cell>
+          <cell r="D28">
+            <v>69532</v>
+          </cell>
+          <cell r="E28">
+            <v>68952</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>70091</v>
+          </cell>
+          <cell r="D29">
+            <v>69233</v>
+          </cell>
+          <cell r="E29">
+            <v>69744</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>71145</v>
+          </cell>
+          <cell r="D30">
+            <v>70349</v>
+          </cell>
+          <cell r="E30">
+            <v>69943</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>72470</v>
+          </cell>
+          <cell r="D31">
+            <v>72151</v>
+          </cell>
+          <cell r="E31">
+            <v>71690</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>74015</v>
+          </cell>
+          <cell r="D32">
+            <v>73614</v>
+          </cell>
+          <cell r="E32">
+            <v>76349</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>75662</v>
+          </cell>
+          <cell r="D33">
+            <v>75419</v>
+          </cell>
+          <cell r="E33">
+            <v>77569</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34">
+            <v>77241</v>
+          </cell>
+          <cell r="D34">
+            <v>78293</v>
+          </cell>
+          <cell r="E34">
+            <v>77506</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35">
+            <v>78590</v>
+          </cell>
+          <cell r="D35">
+            <v>79054</v>
+          </cell>
+          <cell r="E35">
+            <v>78534</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36">
+            <v>79596</v>
+          </cell>
+          <cell r="D36">
+            <v>80346</v>
+          </cell>
+          <cell r="E36">
+            <v>79408</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="לוח 3 table"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="36">
+          <cell r="A36">
+            <v>69</v>
+          </cell>
+          <cell r="B36">
+            <v>932</v>
+          </cell>
+          <cell r="C36">
+            <v>614</v>
+          </cell>
+          <cell r="D36">
+            <v>1221</v>
+          </cell>
+          <cell r="E36">
+            <v>398</v>
+          </cell>
+          <cell r="F36">
+            <v>387</v>
+          </cell>
+          <cell r="G36">
+            <v>337</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>46</v>
+          </cell>
+          <cell r="B37">
+            <v>789</v>
+          </cell>
+          <cell r="C37">
+            <v>629</v>
+          </cell>
+          <cell r="D37">
+            <v>1164</v>
+          </cell>
+          <cell r="E37">
+            <v>513</v>
+          </cell>
+          <cell r="F37">
+            <v>355</v>
+          </cell>
+          <cell r="G37">
+            <v>299</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>30</v>
+          </cell>
+          <cell r="B38">
+            <v>856</v>
+          </cell>
+          <cell r="C38">
+            <v>736</v>
+          </cell>
+          <cell r="D38">
+            <v>1234</v>
+          </cell>
+          <cell r="E38">
+            <v>467</v>
+          </cell>
+          <cell r="F38">
+            <v>362</v>
+          </cell>
+          <cell r="G38">
+            <v>272</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>25</v>
+          </cell>
+          <cell r="B39">
+            <v>684</v>
+          </cell>
+          <cell r="C39">
+            <v>703</v>
+          </cell>
+          <cell r="D39">
+            <v>859</v>
+          </cell>
+          <cell r="E39">
+            <v>459</v>
+          </cell>
+          <cell r="F39">
+            <v>460</v>
+          </cell>
+          <cell r="G39">
+            <v>316</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>37</v>
+          </cell>
+          <cell r="B40">
+            <v>738</v>
+          </cell>
+          <cell r="C40">
+            <v>794</v>
+          </cell>
+          <cell r="D40">
+            <v>970</v>
+          </cell>
+          <cell r="E40">
+            <v>523</v>
+          </cell>
+          <cell r="F40">
+            <v>494</v>
+          </cell>
+          <cell r="G40">
+            <v>365</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>40</v>
+          </cell>
+          <cell r="B41">
+            <v>841</v>
+          </cell>
+          <cell r="C41">
+            <v>920</v>
+          </cell>
+          <cell r="D41">
+            <v>858</v>
+          </cell>
+          <cell r="E41">
+            <v>391</v>
+          </cell>
+          <cell r="F41">
+            <v>442</v>
+          </cell>
+          <cell r="G41">
+            <v>295</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>40</v>
+          </cell>
+          <cell r="B42">
+            <v>1021</v>
+          </cell>
+          <cell r="C42">
+            <v>727</v>
+          </cell>
+          <cell r="D42">
+            <v>827</v>
+          </cell>
+          <cell r="E42">
+            <v>447</v>
+          </cell>
+          <cell r="F42">
+            <v>517</v>
+          </cell>
+          <cell r="G42">
+            <v>443</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>44</v>
+          </cell>
+          <cell r="B43">
+            <v>758</v>
+          </cell>
+          <cell r="C43">
+            <v>710</v>
+          </cell>
+          <cell r="D43">
+            <v>821</v>
+          </cell>
+          <cell r="E43">
+            <v>389</v>
+          </cell>
+          <cell r="F43">
+            <v>356</v>
+          </cell>
+          <cell r="G43">
+            <v>409</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>69</v>
+          </cell>
+          <cell r="B44">
+            <v>944</v>
+          </cell>
+          <cell r="C44">
+            <v>718</v>
+          </cell>
+          <cell r="D44">
+            <v>852</v>
+          </cell>
+          <cell r="E44">
+            <v>483</v>
+          </cell>
+          <cell r="F44">
+            <v>226</v>
+          </cell>
+          <cell r="G44">
+            <v>444</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>39</v>
+          </cell>
+          <cell r="B45">
+            <v>633</v>
+          </cell>
+          <cell r="C45">
+            <v>416</v>
+          </cell>
+          <cell r="D45">
+            <v>610</v>
+          </cell>
+          <cell r="E45">
+            <v>267</v>
+          </cell>
+          <cell r="F45">
+            <v>239</v>
+          </cell>
+          <cell r="G45">
+            <v>194</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>61</v>
+          </cell>
+          <cell r="B46">
+            <v>791</v>
+          </cell>
+          <cell r="C46">
+            <v>562</v>
+          </cell>
+          <cell r="D46">
+            <v>769</v>
+          </cell>
+          <cell r="E46">
+            <v>356</v>
+          </cell>
+          <cell r="F46">
+            <v>333</v>
+          </cell>
+          <cell r="G46">
+            <v>258</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>106</v>
+          </cell>
+          <cell r="B47">
+            <v>1692</v>
+          </cell>
+          <cell r="C47">
+            <v>1331</v>
+          </cell>
+          <cell r="D47">
+            <v>1484</v>
+          </cell>
+          <cell r="E47">
+            <v>721</v>
+          </cell>
+          <cell r="F47">
+            <v>639</v>
+          </cell>
+          <cell r="G47">
+            <v>545</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>46</v>
+          </cell>
+          <cell r="B48">
+            <v>711</v>
+          </cell>
+          <cell r="C48">
+            <v>568</v>
+          </cell>
+          <cell r="D48">
+            <v>979</v>
+          </cell>
+          <cell r="E48">
+            <v>316</v>
+          </cell>
+          <cell r="F48">
+            <v>321</v>
+          </cell>
+          <cell r="G48">
+            <v>251</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>35</v>
+          </cell>
+          <cell r="B49">
+            <v>625</v>
+          </cell>
+          <cell r="C49">
+            <v>579</v>
+          </cell>
+          <cell r="D49">
+            <v>873</v>
+          </cell>
+          <cell r="E49">
+            <v>340</v>
+          </cell>
+          <cell r="F49">
+            <v>243</v>
+          </cell>
+          <cell r="G49">
+            <v>328</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>45</v>
+          </cell>
+          <cell r="B50">
+            <v>642</v>
+          </cell>
+          <cell r="C50">
+            <v>653</v>
+          </cell>
+          <cell r="D50">
+            <v>877</v>
+          </cell>
+          <cell r="E50">
+            <v>334</v>
+          </cell>
+          <cell r="F50">
+            <v>408</v>
+          </cell>
+          <cell r="G50">
+            <v>230</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>25</v>
+          </cell>
+          <cell r="B51">
+            <v>739</v>
+          </cell>
+          <cell r="C51">
+            <v>327</v>
+          </cell>
+          <cell r="D51">
+            <v>701</v>
+          </cell>
+          <cell r="E51">
+            <v>172</v>
+          </cell>
+          <cell r="F51">
+            <v>212</v>
+          </cell>
+          <cell r="G51">
+            <v>159</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>159</v>
+          </cell>
+          <cell r="B90">
+            <v>947</v>
+          </cell>
+          <cell r="C90">
+            <v>676</v>
+          </cell>
+          <cell r="D90">
+            <v>1148</v>
+          </cell>
+          <cell r="E90">
+            <v>902</v>
+          </cell>
+          <cell r="F90">
+            <v>566</v>
+          </cell>
+          <cell r="G90">
+            <v>426</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>168</v>
+          </cell>
+          <cell r="B91">
+            <v>905</v>
+          </cell>
+          <cell r="C91">
+            <v>714</v>
+          </cell>
+          <cell r="D91">
+            <v>1059</v>
+          </cell>
+          <cell r="E91">
+            <v>817</v>
+          </cell>
+          <cell r="F91">
+            <v>504</v>
+          </cell>
+          <cell r="G91">
+            <v>433</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>147</v>
+          </cell>
+          <cell r="B92">
+            <v>915</v>
+          </cell>
+          <cell r="C92">
+            <v>733</v>
+          </cell>
+          <cell r="D92">
+            <v>1126</v>
+          </cell>
+          <cell r="E92">
+            <v>901</v>
+          </cell>
+          <cell r="F92">
+            <v>529</v>
+          </cell>
+          <cell r="G92">
+            <v>442</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>103</v>
+          </cell>
+          <cell r="B93">
+            <v>839</v>
+          </cell>
+          <cell r="C93">
+            <v>685</v>
+          </cell>
+          <cell r="D93">
+            <v>1101</v>
+          </cell>
+          <cell r="E93">
+            <v>763</v>
+          </cell>
+          <cell r="F93">
+            <v>431</v>
+          </cell>
+          <cell r="G93">
+            <v>406</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>162</v>
+          </cell>
+          <cell r="B94">
+            <v>896</v>
+          </cell>
+          <cell r="C94">
+            <v>648</v>
+          </cell>
+          <cell r="D94">
+            <v>1131</v>
+          </cell>
+          <cell r="E94">
+            <v>815</v>
+          </cell>
+          <cell r="F94">
+            <v>524</v>
+          </cell>
+          <cell r="G94">
+            <v>373</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>160</v>
+          </cell>
+          <cell r="B95">
+            <v>996</v>
+          </cell>
+          <cell r="C95">
+            <v>734</v>
+          </cell>
+          <cell r="D95">
+            <v>1171</v>
+          </cell>
+          <cell r="E95">
+            <v>889</v>
+          </cell>
+          <cell r="F95">
+            <v>620</v>
+          </cell>
+          <cell r="G95">
+            <v>454</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>196</v>
+          </cell>
+          <cell r="B96">
+            <v>1103</v>
+          </cell>
+          <cell r="C96">
+            <v>868</v>
+          </cell>
+          <cell r="D96">
+            <v>1292</v>
+          </cell>
+          <cell r="E96">
+            <v>974</v>
+          </cell>
+          <cell r="F96">
+            <v>698</v>
+          </cell>
+          <cell r="G96">
+            <v>546</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>158</v>
+          </cell>
+          <cell r="B97">
+            <v>900</v>
+          </cell>
+          <cell r="C97">
+            <v>671</v>
+          </cell>
+          <cell r="D97">
+            <v>1044</v>
+          </cell>
+          <cell r="E97">
+            <v>793</v>
+          </cell>
+          <cell r="F97">
+            <v>517</v>
+          </cell>
+          <cell r="G97">
+            <v>413</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>193</v>
+          </cell>
+          <cell r="B98">
+            <v>1051</v>
+          </cell>
+          <cell r="C98">
+            <v>753</v>
+          </cell>
+          <cell r="D98">
+            <v>1181</v>
+          </cell>
+          <cell r="E98">
+            <v>1059</v>
+          </cell>
+          <cell r="F98">
+            <v>541</v>
+          </cell>
+          <cell r="G98">
+            <v>486</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>86</v>
+          </cell>
+          <cell r="B99">
+            <v>669</v>
+          </cell>
+          <cell r="C99">
+            <v>485</v>
+          </cell>
+          <cell r="D99">
+            <v>731</v>
+          </cell>
+          <cell r="E99">
+            <v>586</v>
+          </cell>
+          <cell r="F99">
+            <v>358</v>
+          </cell>
+          <cell r="G99">
+            <v>277</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>120</v>
+          </cell>
+          <cell r="B100">
+            <v>934</v>
+          </cell>
+          <cell r="C100">
+            <v>689</v>
+          </cell>
+          <cell r="D100">
+            <v>1035</v>
+          </cell>
+          <cell r="E100">
+            <v>745</v>
+          </cell>
+          <cell r="F100">
+            <v>477</v>
+          </cell>
+          <cell r="G100">
+            <v>415</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>186</v>
+          </cell>
+          <cell r="B101">
+            <v>1164</v>
+          </cell>
+          <cell r="C101">
+            <v>916</v>
+          </cell>
+          <cell r="D101">
+            <v>1343</v>
+          </cell>
+          <cell r="E101">
+            <v>970</v>
+          </cell>
+          <cell r="F101">
+            <v>674</v>
+          </cell>
+          <cell r="G101">
+            <v>528</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>151</v>
+          </cell>
+          <cell r="B102">
+            <v>1030</v>
+          </cell>
+          <cell r="C102">
+            <v>731</v>
+          </cell>
+          <cell r="D102">
+            <v>1156</v>
+          </cell>
+          <cell r="E102">
+            <v>819</v>
+          </cell>
+          <cell r="F102">
+            <v>710</v>
+          </cell>
+          <cell r="G102">
+            <v>476</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>172</v>
+          </cell>
+          <cell r="B103">
+            <v>950</v>
+          </cell>
+          <cell r="C103">
+            <v>717</v>
+          </cell>
+          <cell r="D103">
+            <v>1114</v>
+          </cell>
+          <cell r="E103">
+            <v>793</v>
+          </cell>
+          <cell r="F103">
+            <v>592</v>
+          </cell>
+          <cell r="G103">
+            <v>454</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>161</v>
+          </cell>
+          <cell r="B104">
+            <v>1033</v>
+          </cell>
+          <cell r="C104">
+            <v>791</v>
+          </cell>
+          <cell r="D104">
+            <v>1230</v>
+          </cell>
+          <cell r="E104">
+            <v>859</v>
+          </cell>
+          <cell r="F104">
+            <v>535</v>
+          </cell>
+          <cell r="G104">
+            <v>502</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>112</v>
+          </cell>
+          <cell r="B105">
+            <v>792</v>
+          </cell>
+          <cell r="C105">
+            <v>644</v>
+          </cell>
+          <cell r="D105">
+            <v>928</v>
+          </cell>
+          <cell r="E105">
+            <v>697</v>
+          </cell>
+          <cell r="F105">
+            <v>436</v>
+          </cell>
+          <cell r="G105">
+            <v>318</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2242,1550 +4163,1727 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="8">
         <v>2023</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="8">
         <v>1</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="9">
         <v>3.75</v>
       </c>
-      <c r="G14" s="1">
-        <v>7102</v>
-      </c>
-      <c r="H14" s="1">
-        <v>6377</v>
-      </c>
-      <c r="I14" s="1">
-        <v>6692</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="G14" s="7">
+        <f>'[1]לוח 1 table'!$M13</f>
+        <v>7100</v>
+      </c>
+      <c r="H14" s="7">
+        <f>'[1]לוח 1 table'!$L13</f>
+        <v>6378</v>
+      </c>
+      <c r="I14" s="7">
+        <f>'[1]לוח 1 table'!$K13</f>
+        <v>6679</v>
+      </c>
+      <c r="J14" s="7">
+        <f>'[1]לוח 1 table'!$I13</f>
         <v>2500</v>
       </c>
-      <c r="K14" s="1">
-        <v>2147</v>
-      </c>
-      <c r="L14" s="1">
-        <v>2385</v>
-      </c>
-      <c r="M14" s="1">
-        <v>4602</v>
-      </c>
-      <c r="N14" s="1">
-        <v>4231</v>
-      </c>
-      <c r="O14" s="1">
-        <v>4243</v>
-      </c>
-      <c r="P14" s="1">
+      <c r="K14" s="7">
+        <f>'[1]לוח 1 table'!$H13</f>
+        <v>2150</v>
+      </c>
+      <c r="L14" s="7">
+        <f>'[1]לוח 1 table'!$G13</f>
+        <v>2384</v>
+      </c>
+      <c r="M14" s="7">
+        <f>'[1]לוח 1 table'!$D13</f>
+        <v>4600</v>
+      </c>
+      <c r="N14" s="7">
+        <f>'[1]לוח 1 table'!$C13</f>
+        <v>4229</v>
+      </c>
+      <c r="O14" s="7">
+        <f>'[1]לוח 1 table'!$B13</f>
+        <v>4239</v>
+      </c>
+      <c r="P14" s="7">
+        <f>'[2]2'!$E9</f>
         <v>54118</v>
       </c>
-      <c r="Q14" s="1">
-        <v>52618</v>
-      </c>
-      <c r="R14" s="1">
-        <v>52332</v>
-      </c>
-      <c r="S14" s="1">
+      <c r="Q14" s="7">
+        <f>'[2]2'!$D9</f>
+        <v>52606</v>
+      </c>
+      <c r="R14" s="7">
+        <f>'[2]2'!$C9</f>
+        <v>52324</v>
+      </c>
+      <c r="S14" s="7">
         <v>913</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="8">
         <v>508</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="8">
         <v>405</v>
       </c>
-      <c r="V14" s="1">
+      <c r="V14" s="7">
         <v>857</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="8">
         <v>207</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="8">
         <v>650</v>
       </c>
-      <c r="Y14" s="1">
+      <c r="Y14" s="7">
         <v>1226</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="8">
         <v>417</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="8">
         <v>809</v>
       </c>
-      <c r="AB14" s="1">
+      <c r="AB14" s="7">
         <v>1415</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="8">
         <v>467</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="8">
         <v>948</v>
       </c>
-      <c r="AE14" s="1">
+      <c r="AE14" s="7">
         <v>1015</v>
       </c>
-      <c r="AF14">
+      <c r="AF14" s="8">
         <v>353</v>
       </c>
-      <c r="AG14">
+      <c r="AG14" s="8">
         <v>662</v>
       </c>
-      <c r="AH14" s="1">
+      <c r="AH14" s="7">
         <v>1459</v>
       </c>
-      <c r="AI14">
+      <c r="AI14" s="8">
         <v>488</v>
       </c>
-      <c r="AJ14">
+      <c r="AJ14" s="8">
         <v>971</v>
       </c>
-      <c r="AK14" s="1">
+      <c r="AK14" s="7">
         <v>216</v>
       </c>
-      <c r="AL14">
+      <c r="AL14" s="8">
         <v>59</v>
       </c>
-      <c r="AM14">
+      <c r="AM14" s="8">
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="8">
         <v>2023</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="8">
         <v>2</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="9">
         <v>4.25</v>
       </c>
-      <c r="G15" s="1">
-        <v>6338</v>
-      </c>
-      <c r="H15" s="1">
-        <v>6546</v>
-      </c>
-      <c r="I15" s="1">
-        <v>6464</v>
-      </c>
-      <c r="J15" s="1">
-        <v>2443</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2577</v>
-      </c>
-      <c r="L15" s="1">
-        <v>2343</v>
-      </c>
-      <c r="M15" s="1">
+      <c r="G15" s="7">
+        <f>'[1]לוח 1 table'!$M14</f>
+        <v>6336</v>
+      </c>
+      <c r="H15" s="7">
+        <f>'[1]לוח 1 table'!$L14</f>
+        <v>6530</v>
+      </c>
+      <c r="I15" s="7">
+        <f>'[1]לוח 1 table'!$K14</f>
+        <v>6450</v>
+      </c>
+      <c r="J15" s="7">
+        <f>'[1]לוח 1 table'!$I14</f>
+        <v>2441</v>
+      </c>
+      <c r="K15" s="7">
+        <f>'[1]לוח 1 table'!$H14</f>
+        <v>2561</v>
+      </c>
+      <c r="L15" s="7">
+        <f>'[1]לוח 1 table'!$G14</f>
+        <v>2337</v>
+      </c>
+      <c r="M15" s="7">
+        <f>'[1]לוח 1 table'!$D14</f>
         <v>3895</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N15" s="7">
+        <f>'[1]לוח 1 table'!$C14</f>
         <v>3969</v>
       </c>
-      <c r="O15" s="1">
-        <v>4081</v>
-      </c>
-      <c r="P15" s="1">
+      <c r="O15" s="7">
+        <f>'[1]לוח 1 table'!$B14</f>
+        <v>4078</v>
+      </c>
+      <c r="P15" s="7">
+        <f>'[2]2'!$E10</f>
         <v>54457</v>
       </c>
-      <c r="Q15" s="1">
-        <v>55255</v>
-      </c>
-      <c r="R15" s="1">
-        <v>53357</v>
-      </c>
-      <c r="S15" s="1">
+      <c r="Q15" s="7">
+        <f>'[2]2'!$D10</f>
+        <v>55306</v>
+      </c>
+      <c r="R15" s="7">
+        <f>'[2]2'!$C10</f>
+        <v>53345</v>
+      </c>
+      <c r="S15" s="7">
         <v>722</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="8">
         <v>373</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="8">
         <v>349</v>
       </c>
-      <c r="V15" s="1">
+      <c r="V15" s="7">
         <v>686</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="8">
         <v>165</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="8">
         <v>521</v>
       </c>
-      <c r="Y15" s="1">
+      <c r="Y15" s="7">
         <v>1023</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="8">
         <v>264</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="8">
         <v>759</v>
       </c>
-      <c r="AB15" s="1">
+      <c r="AB15" s="7">
         <v>1170</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="8">
         <v>383</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="8">
         <v>787</v>
       </c>
-      <c r="AE15" s="1">
+      <c r="AE15" s="7">
         <v>1036</v>
       </c>
-      <c r="AF15">
+      <c r="AF15" s="8">
         <v>477</v>
       </c>
-      <c r="AG15">
+      <c r="AG15" s="8">
         <v>559</v>
       </c>
-      <c r="AH15" s="1">
+      <c r="AH15" s="7">
         <v>1509</v>
       </c>
-      <c r="AI15">
+      <c r="AI15" s="8">
         <v>711</v>
       </c>
-      <c r="AJ15">
+      <c r="AJ15" s="8">
         <v>798</v>
       </c>
-      <c r="AK15" s="1">
+      <c r="AK15" s="7">
         <v>193</v>
       </c>
-      <c r="AL15">
+      <c r="AL15" s="8">
         <v>70</v>
       </c>
-      <c r="AM15">
+      <c r="AM15" s="8">
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="8">
         <v>2023</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="8">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="9">
         <v>4.25</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="7">
+        <f>'[1]לוח 1 table'!$M15</f>
         <v>7223</v>
       </c>
-      <c r="H16" s="1">
-        <v>6310</v>
-      </c>
-      <c r="I16" s="1">
-        <v>6287</v>
-      </c>
-      <c r="J16" s="1">
-        <v>2729</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2329</v>
-      </c>
-      <c r="L16" s="1">
-        <v>2329</v>
-      </c>
-      <c r="M16" s="1">
-        <v>4494</v>
-      </c>
-      <c r="N16" s="1">
-        <v>3981</v>
-      </c>
-      <c r="O16" s="1">
+      <c r="H16" s="7">
+        <f>'[1]לוח 1 table'!$L15</f>
+        <v>6270</v>
+      </c>
+      <c r="I16" s="7">
+        <f>'[1]לוח 1 table'!$K15</f>
+        <v>6275</v>
+      </c>
+      <c r="J16" s="7">
+        <f>'[1]לוח 1 table'!$I15</f>
+        <v>2727</v>
+      </c>
+      <c r="K16" s="7">
+        <f>'[1]לוח 1 table'!$H15</f>
+        <v>2303</v>
+      </c>
+      <c r="L16" s="7">
+        <f>'[1]לוח 1 table'!$G15</f>
+        <v>2321</v>
+      </c>
+      <c r="M16" s="7">
+        <f>'[1]לוח 1 table'!$D15</f>
+        <v>4496</v>
+      </c>
+      <c r="N16" s="7">
+        <f>'[1]לוח 1 table'!$C15</f>
+        <v>3967</v>
+      </c>
+      <c r="O16" s="7">
+        <f>'[1]לוח 1 table'!$B15</f>
         <v>3936</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="7">
+        <f>'[2]2'!$E11</f>
         <v>54096</v>
       </c>
-      <c r="Q16" s="1">
-        <v>53984</v>
-      </c>
-      <c r="R16" s="1">
-        <v>54399</v>
-      </c>
-      <c r="S16" s="1">
+      <c r="Q16" s="7">
+        <f>'[2]2'!$D11</f>
+        <v>53978</v>
+      </c>
+      <c r="R16" s="7">
+        <f>'[2]2'!$C11</f>
+        <v>54382</v>
+      </c>
+      <c r="S16" s="7">
         <v>686</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="8">
         <v>300</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="8">
         <v>386</v>
       </c>
-      <c r="V16" s="1">
+      <c r="V16" s="7">
         <v>943</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="8">
         <v>243</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="8">
         <v>700</v>
       </c>
-      <c r="Y16" s="1">
+      <c r="Y16" s="7">
         <v>1233</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="8">
         <v>275</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="8">
         <v>958</v>
       </c>
-      <c r="AB16" s="1">
+      <c r="AB16" s="7">
         <v>1207</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="8">
         <v>369</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="8">
         <v>838</v>
       </c>
-      <c r="AE16" s="1">
+      <c r="AE16" s="7">
         <v>1042</v>
       </c>
-      <c r="AF16">
+      <c r="AF16" s="8">
         <v>443</v>
       </c>
-      <c r="AG16">
+      <c r="AG16" s="8">
         <v>599</v>
       </c>
-      <c r="AH16" s="1">
+      <c r="AH16" s="7">
         <v>1909</v>
       </c>
-      <c r="AI16">
+      <c r="AI16" s="8">
         <v>1052</v>
       </c>
-      <c r="AJ16">
+      <c r="AJ16" s="8">
         <v>857</v>
       </c>
-      <c r="AK16" s="1">
+      <c r="AK16" s="7">
         <v>203</v>
       </c>
-      <c r="AL16">
+      <c r="AL16" s="8">
         <v>47</v>
       </c>
-      <c r="AM16">
+      <c r="AM16" s="8">
         <v>156</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="8">
         <v>2023</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="8">
         <v>4</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="9">
         <v>4.5</v>
       </c>
-      <c r="G17" s="1">
-        <v>4152</v>
-      </c>
-      <c r="H17" s="1">
-        <v>6085</v>
-      </c>
-      <c r="I17" s="1">
-        <v>6178</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1457</v>
-      </c>
-      <c r="K17" s="1">
-        <v>2315</v>
-      </c>
-      <c r="L17" s="1">
-        <v>2344</v>
-      </c>
-      <c r="M17" s="1">
+      <c r="G17" s="7">
+        <f>'[1]לוח 1 table'!$M16</f>
+        <v>4151</v>
+      </c>
+      <c r="H17" s="7">
+        <f>'[1]לוח 1 table'!$L16</f>
+        <v>6098</v>
+      </c>
+      <c r="I17" s="7">
+        <f>'[1]לוח 1 table'!$K16</f>
+        <v>6172</v>
+      </c>
+      <c r="J17" s="7">
+        <f>'[1]לוח 1 table'!$I16</f>
+        <v>1456</v>
+      </c>
+      <c r="K17" s="7">
+        <f>'[1]לוח 1 table'!$H16</f>
+        <v>2323</v>
+      </c>
+      <c r="L17" s="7">
+        <f>'[1]לוח 1 table'!$G16</f>
+        <v>2338</v>
+      </c>
+      <c r="M17" s="7">
+        <f>'[1]לוח 1 table'!$D16</f>
         <v>2695</v>
       </c>
-      <c r="N17" s="1">
-        <v>3770</v>
-      </c>
-      <c r="O17" s="1">
-        <v>3808</v>
-      </c>
-      <c r="P17" s="1">
+      <c r="N17" s="7">
+        <f>'[1]לוח 1 table'!$C16</f>
+        <v>3775</v>
+      </c>
+      <c r="O17" s="7">
+        <f>'[1]לוח 1 table'!$B16</f>
+        <v>3811</v>
+      </c>
+      <c r="P17" s="7">
+        <f>'[2]2'!$E12</f>
         <v>55672</v>
       </c>
-      <c r="Q17" s="1">
-        <v>55490</v>
-      </c>
-      <c r="R17" s="1">
-        <v>55455</v>
-      </c>
-      <c r="S17" s="1">
+      <c r="Q17" s="7">
+        <f>'[2]2'!$D12</f>
+        <v>55493</v>
+      </c>
+      <c r="R17" s="7">
+        <f>'[2]2'!$C12</f>
+        <v>55435</v>
+      </c>
+      <c r="S17" s="7">
         <v>359</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="8">
         <v>141</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="8">
         <v>218</v>
       </c>
-      <c r="V17" s="1">
+      <c r="V17" s="7">
         <v>652</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="8">
         <v>206</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="8">
         <v>446</v>
       </c>
-      <c r="Y17" s="1">
+      <c r="Y17" s="7">
         <v>675</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="8">
         <v>148</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="8">
         <v>527</v>
       </c>
-      <c r="AB17" s="1">
+      <c r="AB17" s="7">
         <v>876</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="8">
         <v>377</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="8">
         <v>499</v>
       </c>
-      <c r="AE17" s="1">
+      <c r="AE17" s="7">
         <v>540</v>
       </c>
-      <c r="AF17">
+      <c r="AF17" s="8">
         <v>176</v>
       </c>
-      <c r="AG17">
+      <c r="AG17" s="8">
         <v>364</v>
       </c>
-      <c r="AH17" s="1">
+      <c r="AH17" s="7">
         <v>924</v>
       </c>
-      <c r="AI17">
+      <c r="AI17" s="8">
         <v>354</v>
       </c>
-      <c r="AJ17">
+      <c r="AJ17" s="8">
         <v>570</v>
       </c>
-      <c r="AK17" s="1">
+      <c r="AK17" s="7">
         <v>127</v>
       </c>
-      <c r="AL17">
+      <c r="AL17" s="8">
         <v>56</v>
       </c>
-      <c r="AM17">
+      <c r="AM17" s="8">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="8">
         <v>2023</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>5</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="9">
         <v>4.75</v>
       </c>
-      <c r="G18" s="1">
-        <v>6220</v>
-      </c>
-      <c r="H18" s="1">
-        <v>6112</v>
-      </c>
-      <c r="I18" s="1">
-        <v>6160</v>
-      </c>
-      <c r="J18" s="1">
-        <v>2226</v>
-      </c>
-      <c r="K18" s="1">
-        <v>2382</v>
-      </c>
-      <c r="L18" s="1">
-        <v>2386</v>
-      </c>
-      <c r="M18" s="1">
+      <c r="G18" s="7">
+        <f>'[1]לוח 1 table'!$M17</f>
+        <v>6219</v>
+      </c>
+      <c r="H18" s="7">
+        <f>'[1]לוח 1 table'!$L17</f>
+        <v>6118</v>
+      </c>
+      <c r="I18" s="7">
+        <f>'[1]לוח 1 table'!$K17</f>
+        <v>6158</v>
+      </c>
+      <c r="J18" s="7">
+        <f>'[1]לוח 1 table'!$I17</f>
+        <v>2225</v>
+      </c>
+      <c r="K18" s="7">
+        <f>'[1]לוח 1 table'!$H17</f>
+        <v>2380</v>
+      </c>
+      <c r="L18" s="7">
+        <f>'[1]לוח 1 table'!$G17</f>
+        <v>2383</v>
+      </c>
+      <c r="M18" s="7">
+        <f>'[1]לוח 1 table'!$D17</f>
         <v>3994</v>
       </c>
-      <c r="N18" s="1">
-        <v>3731</v>
-      </c>
-      <c r="O18" s="1">
-        <v>3702</v>
-      </c>
-      <c r="P18" s="1">
+      <c r="N18" s="7">
+        <f>'[1]לוח 1 table'!$C17</f>
+        <v>3738</v>
+      </c>
+      <c r="O18" s="7">
+        <f>'[1]לוח 1 table'!$B17</f>
+        <v>3706</v>
+      </c>
+      <c r="P18" s="7">
+        <f>'[2]2'!$E13</f>
         <v>56899</v>
       </c>
-      <c r="Q18" s="1">
-        <v>56870</v>
-      </c>
-      <c r="R18" s="1">
-        <v>56538</v>
-      </c>
-      <c r="S18" s="1">
+      <c r="Q18" s="7">
+        <f>'[2]2'!$D13</f>
+        <v>56838</v>
+      </c>
+      <c r="R18" s="7">
+        <f>'[2]2'!$C13</f>
+        <v>56518</v>
+      </c>
+      <c r="S18" s="7">
         <v>520</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="8">
         <v>139</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="8">
         <v>381</v>
       </c>
-      <c r="V18" s="1">
+      <c r="V18" s="7">
         <v>913</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="8">
         <v>318</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="8">
         <v>595</v>
       </c>
-      <c r="Y18" s="1">
+      <c r="Y18" s="7">
         <v>964</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="8">
         <v>247</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="8">
         <v>717</v>
       </c>
-      <c r="AB18" s="1">
+      <c r="AB18" s="7">
         <v>1438</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="8">
         <v>613</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="8">
         <v>825</v>
       </c>
-      <c r="AE18" s="1">
+      <c r="AE18" s="7">
         <v>904</v>
       </c>
-      <c r="AF18">
+      <c r="AF18" s="8">
         <v>345</v>
       </c>
-      <c r="AG18">
+      <c r="AG18" s="8">
         <v>559</v>
       </c>
-      <c r="AH18" s="1">
+      <c r="AH18" s="7">
         <v>1223</v>
       </c>
-      <c r="AI18">
+      <c r="AI18" s="8">
         <v>445</v>
       </c>
-      <c r="AJ18">
+      <c r="AJ18" s="8">
         <v>778</v>
       </c>
-      <c r="AK18" s="1">
+      <c r="AK18" s="7">
         <v>257</v>
       </c>
-      <c r="AL18">
+      <c r="AL18" s="8">
         <v>119</v>
       </c>
-      <c r="AM18">
+      <c r="AM18" s="8">
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="8">
         <v>2023</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="8">
         <v>6</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="9">
         <v>4.75</v>
       </c>
-      <c r="G19" s="1">
-        <v>7053</v>
-      </c>
-      <c r="H19" s="1">
-        <v>6212</v>
-      </c>
-      <c r="I19" s="1">
+      <c r="G19" s="7">
+        <f>'[1]לוח 1 table'!$M18</f>
+        <v>7052</v>
+      </c>
+      <c r="H19" s="7">
+        <f>'[1]לוח 1 table'!$L18</f>
+        <v>6215</v>
+      </c>
+      <c r="I19" s="7">
+        <f>'[1]לוח 1 table'!$K18</f>
         <v>6240</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="7">
+        <f>'[1]לוח 1 table'!$I18</f>
         <v>2829</v>
       </c>
-      <c r="K19" s="1">
-        <v>2457</v>
-      </c>
-      <c r="L19" s="1">
-        <v>2451</v>
-      </c>
-      <c r="M19" s="1">
-        <v>4224</v>
-      </c>
-      <c r="N19" s="1">
-        <v>3755</v>
-      </c>
-      <c r="O19" s="1">
-        <v>3623</v>
-      </c>
-      <c r="P19" s="1">
+      <c r="K19" s="7">
+        <f>'[1]לוח 1 table'!$H18</f>
+        <v>2453</v>
+      </c>
+      <c r="L19" s="7">
+        <f>'[1]לוח 1 table'!$G18</f>
+        <v>2452</v>
+      </c>
+      <c r="M19" s="7">
+        <f>'[1]לוח 1 table'!$D18</f>
+        <v>4223</v>
+      </c>
+      <c r="N19" s="7">
+        <f>'[1]לוח 1 table'!$C18</f>
+        <v>3761</v>
+      </c>
+      <c r="O19" s="7">
+        <f>'[1]לוח 1 table'!$B18</f>
+        <v>3627</v>
+      </c>
+      <c r="P19" s="7">
+        <f>'[2]2'!$E14</f>
         <v>57098</v>
       </c>
-      <c r="Q19" s="1">
-        <v>57650</v>
-      </c>
-      <c r="R19" s="1">
-        <v>57663</v>
-      </c>
-      <c r="S19" s="1">
+      <c r="Q19" s="7">
+        <f>'[2]2'!$D14</f>
+        <v>57609</v>
+      </c>
+      <c r="R19" s="7">
+        <f>'[2]2'!$C14</f>
+        <v>57647</v>
+      </c>
+      <c r="S19" s="7">
         <v>669</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="8">
         <v>295</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="8">
         <v>374</v>
       </c>
-      <c r="V19" s="1">
+      <c r="V19" s="7">
         <v>949</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="8">
         <v>316</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="8">
         <v>633</v>
       </c>
-      <c r="Y19" s="1">
+      <c r="Y19" s="7">
         <v>1020</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="8">
         <v>257</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="8">
         <v>763</v>
       </c>
-      <c r="AB19" s="1">
+      <c r="AB19" s="7">
         <v>1618</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="8">
         <v>764</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="8">
         <v>854</v>
       </c>
-      <c r="AE19" s="1">
+      <c r="AE19" s="7">
         <v>1037</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="8">
         <v>431</v>
       </c>
-      <c r="AG19">
+      <c r="AG19" s="8">
         <v>606</v>
       </c>
-      <c r="AH19" s="1">
+      <c r="AH19" s="7">
         <v>1545</v>
       </c>
-      <c r="AI19">
+      <c r="AI19" s="8">
         <v>711</v>
       </c>
-      <c r="AJ19">
+      <c r="AJ19" s="8">
         <v>834</v>
       </c>
-      <c r="AK19" s="1">
+      <c r="AK19" s="7">
         <v>213</v>
       </c>
-      <c r="AL19">
+      <c r="AL19" s="8">
         <v>55</v>
       </c>
-      <c r="AM19">
+      <c r="AM19" s="8">
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="8">
         <v>2023</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="8">
         <v>7</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="9">
         <v>4.75</v>
       </c>
-      <c r="G20" s="1">
-        <v>6562</v>
-      </c>
-      <c r="H20" s="1">
-        <v>6039</v>
-      </c>
-      <c r="I20" s="1">
-        <v>6411</v>
-      </c>
-      <c r="J20" s="1">
-        <v>2506</v>
-      </c>
-      <c r="K20" s="1">
-        <v>2452</v>
-      </c>
-      <c r="L20" s="1">
-        <v>2533</v>
-      </c>
-      <c r="M20" s="1">
-        <v>4056</v>
-      </c>
-      <c r="N20" s="1">
-        <v>3588</v>
-      </c>
-      <c r="O20" s="1">
-        <v>3578</v>
-      </c>
-      <c r="P20" s="1">
+      <c r="G20" s="7">
+        <f>'[1]לוח 1 table'!$M19</f>
+        <v>6558</v>
+      </c>
+      <c r="H20" s="7">
+        <f>'[1]לוח 1 table'!$L19</f>
+        <v>6043</v>
+      </c>
+      <c r="I20" s="7">
+        <f>'[1]לוח 1 table'!$K19</f>
+        <v>6410</v>
+      </c>
+      <c r="J20" s="7">
+        <f>'[1]לוח 1 table'!$I19</f>
+        <v>2503</v>
+      </c>
+      <c r="K20" s="7">
+        <f>'[1]לוח 1 table'!$H19</f>
+        <v>2450</v>
+      </c>
+      <c r="L20" s="7">
+        <f>'[1]לוח 1 table'!$G19</f>
+        <v>2537</v>
+      </c>
+      <c r="M20" s="7">
+        <f>'[1]לוח 1 table'!$D19</f>
+        <v>4055</v>
+      </c>
+      <c r="N20" s="7">
+        <f>'[1]לוח 1 table'!$C19</f>
+        <v>3593</v>
+      </c>
+      <c r="O20" s="7">
+        <f>'[1]לוח 1 table'!$B19</f>
+        <v>3580</v>
+      </c>
+      <c r="P20" s="7">
+        <f>'[2]2'!$E15</f>
         <v>58404</v>
       </c>
-      <c r="Q20" s="1">
-        <v>58731</v>
-      </c>
-      <c r="R20" s="1">
-        <v>58840</v>
-      </c>
-      <c r="S20" s="1">
+      <c r="Q20" s="7">
+        <f>'[2]2'!$D15</f>
+        <v>58719</v>
+      </c>
+      <c r="R20" s="7">
+        <f>'[2]2'!$C15</f>
+        <v>58832</v>
+      </c>
+      <c r="S20" s="7">
         <v>559</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="8">
         <v>178</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="8">
         <v>381</v>
       </c>
-      <c r="V20" s="1">
+      <c r="V20" s="7">
         <v>898</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="8">
         <v>348</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="8">
         <v>550</v>
       </c>
-      <c r="Y20" s="1">
+      <c r="Y20" s="7">
         <v>931</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="8">
         <v>245</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="8">
         <v>686</v>
       </c>
-      <c r="AB20" s="1">
+      <c r="AB20" s="7">
         <v>1344</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="8">
         <v>496</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="8">
         <v>848</v>
       </c>
-      <c r="AE20" s="1">
+      <c r="AE20" s="7">
         <v>1065</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="8">
         <v>445</v>
       </c>
-      <c r="AG20">
+      <c r="AG20" s="8">
         <v>620</v>
       </c>
-      <c r="AH20" s="1">
+      <c r="AH20" s="7">
         <v>1589</v>
       </c>
-      <c r="AI20">
+      <c r="AI20" s="8">
         <v>749</v>
       </c>
-      <c r="AJ20">
+      <c r="AJ20" s="8">
         <v>840</v>
       </c>
-      <c r="AK20" s="1">
+      <c r="AK20" s="7">
         <v>176</v>
       </c>
-      <c r="AL20">
+      <c r="AL20" s="8">
         <v>45</v>
       </c>
-      <c r="AM20">
+      <c r="AM20" s="8">
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="8">
         <v>2023</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="8">
         <v>8</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="9">
         <v>4.75</v>
       </c>
-      <c r="G21" s="1">
-        <v>7557</v>
-      </c>
-      <c r="H21" s="1">
-        <v>7215</v>
-      </c>
-      <c r="I21" s="1">
-        <v>6653</v>
-      </c>
-      <c r="J21" s="1">
-        <v>3213</v>
-      </c>
-      <c r="K21" s="1">
-        <v>3118</v>
-      </c>
-      <c r="L21" s="1">
-        <v>2630</v>
-      </c>
-      <c r="M21" s="1">
-        <v>4344</v>
-      </c>
-      <c r="N21" s="1">
-        <v>4097</v>
-      </c>
-      <c r="O21" s="1">
+      <c r="G21" s="7">
+        <f>'[1]לוח 1 table'!$M20</f>
+        <v>7546</v>
+      </c>
+      <c r="H21" s="7">
+        <f>'[1]לוח 1 table'!$L20</f>
+        <v>7211</v>
+      </c>
+      <c r="I21" s="7">
+        <f>'[1]לוח 1 table'!$K20</f>
+        <v>6649</v>
+      </c>
+      <c r="J21" s="7">
+        <f>'[1]לוח 1 table'!$I20</f>
+        <v>3201</v>
+      </c>
+      <c r="K21" s="7">
+        <f>'[1]לוח 1 table'!$H20</f>
+        <v>3109</v>
+      </c>
+      <c r="L21" s="7">
+        <f>'[1]לוח 1 table'!$G20</f>
+        <v>2634</v>
+      </c>
+      <c r="M21" s="7">
+        <f>'[1]לוח 1 table'!$D20</f>
+        <v>4345</v>
+      </c>
+      <c r="N21" s="7">
+        <f>'[1]לוח 1 table'!$C20</f>
+        <v>4103</v>
+      </c>
+      <c r="O21" s="7">
+        <f>'[1]לוח 1 table'!$B20</f>
         <v>3573</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="7">
+        <f>'[2]2'!$E16</f>
         <v>58705</v>
       </c>
-      <c r="Q21" s="1">
-        <v>59096</v>
-      </c>
-      <c r="R21" s="1">
-        <v>60064</v>
-      </c>
-      <c r="S21" s="1">
+      <c r="Q21" s="7">
+        <f>'[2]2'!$D16</f>
+        <v>59117</v>
+      </c>
+      <c r="R21" s="7">
+        <f>'[2]2'!$C16</f>
+        <v>60067</v>
+      </c>
+      <c r="S21" s="7">
         <v>683</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="8">
         <v>321</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="8">
         <v>362</v>
       </c>
-      <c r="V21" s="1">
+      <c r="V21" s="7">
         <v>903</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="8">
         <v>366</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="8">
         <v>537</v>
       </c>
-      <c r="Y21" s="1">
+      <c r="Y21" s="7">
         <v>1210</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="8">
         <v>290</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="8">
         <v>920</v>
       </c>
-      <c r="AB21" s="1">
+      <c r="AB21" s="7">
         <v>1535</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="8">
         <v>679</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="8">
         <v>856</v>
       </c>
-      <c r="AE21" s="1">
+      <c r="AE21" s="7">
         <v>1103</v>
       </c>
-      <c r="AF21">
+      <c r="AF21" s="8">
         <v>469</v>
       </c>
-      <c r="AG21">
+      <c r="AG21" s="8">
         <v>634</v>
       </c>
-      <c r="AH21" s="1">
+      <c r="AH21" s="7">
         <v>1940</v>
       </c>
-      <c r="AI21">
+      <c r="AI21" s="8">
         <v>1034</v>
       </c>
-      <c r="AJ21">
+      <c r="AJ21" s="8">
         <v>906</v>
       </c>
-      <c r="AK21" s="1">
+      <c r="AK21" s="7">
         <v>182</v>
       </c>
-      <c r="AL21">
+      <c r="AL21" s="8">
         <v>54</v>
       </c>
-      <c r="AM21">
+      <c r="AM21" s="8">
         <v>128</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="8">
         <v>2023</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="8">
         <v>9</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="9">
         <v>4.75</v>
       </c>
-      <c r="G22" s="1">
-        <v>5861</v>
-      </c>
-      <c r="H22" s="1">
-        <v>6492</v>
-      </c>
-      <c r="I22" s="1">
-        <v>6932</v>
-      </c>
-      <c r="J22" s="1">
-        <v>2394</v>
-      </c>
-      <c r="K22" s="1">
-        <v>2851</v>
-      </c>
-      <c r="L22" s="1">
-        <v>2743</v>
-      </c>
-      <c r="M22" s="1">
-        <v>3467</v>
-      </c>
-      <c r="N22" s="1">
-        <v>3641</v>
-      </c>
-      <c r="O22" s="1">
-        <v>3615</v>
-      </c>
-      <c r="P22" s="1">
+      <c r="G22" s="7">
+        <f>'[1]לוח 1 table'!$M21</f>
+        <v>5857</v>
+      </c>
+      <c r="H22" s="7">
+        <f>'[1]לוח 1 table'!$L21</f>
+        <v>6502</v>
+      </c>
+      <c r="I22" s="7">
+        <f>'[1]לוח 1 table'!$K21</f>
+        <v>6926</v>
+      </c>
+      <c r="J22" s="7">
+        <f>'[1]לוח 1 table'!$I21</f>
+        <v>2389</v>
+      </c>
+      <c r="K22" s="7">
+        <f>'[1]לוח 1 table'!$H21</f>
+        <v>2869</v>
+      </c>
+      <c r="L22" s="7">
+        <f>'[1]לוח 1 table'!$G21</f>
+        <v>2745</v>
+      </c>
+      <c r="M22" s="7">
+        <f>'[1]לוח 1 table'!$D21</f>
+        <v>3468</v>
+      </c>
+      <c r="N22" s="7">
+        <f>'[1]לוח 1 table'!$C21</f>
+        <v>3634</v>
+      </c>
+      <c r="O22" s="7">
+        <f>'[1]לוח 1 table'!$B21</f>
+        <v>3611</v>
+      </c>
+      <c r="P22" s="7">
+        <f>'[2]2'!$E17</f>
         <v>61068</v>
       </c>
-      <c r="Q22" s="1">
-        <v>61696</v>
-      </c>
-      <c r="R22" s="1">
-        <v>61309</v>
-      </c>
-      <c r="S22" s="1">
+      <c r="Q22" s="7">
+        <f>'[2]2'!$D17</f>
+        <v>61739</v>
+      </c>
+      <c r="R22" s="7">
+        <f>'[2]2'!$C17</f>
+        <v>61324</v>
+      </c>
+      <c r="S22" s="7">
         <v>685</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="8">
         <v>365</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="8">
         <v>320</v>
       </c>
-      <c r="V22" s="1">
+      <c r="V22" s="7">
         <v>659</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="8">
         <v>192</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="8">
         <v>467</v>
       </c>
-      <c r="Y22" s="1">
+      <c r="Y22" s="7">
         <v>873</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="8">
         <v>271</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="8">
         <v>602</v>
       </c>
-      <c r="AB22" s="1">
+      <c r="AB22" s="7">
         <v>1336</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="8">
         <v>550</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="8">
         <v>786</v>
       </c>
-      <c r="AE22" s="1">
+      <c r="AE22" s="7">
         <v>890</v>
       </c>
-      <c r="AF22">
+      <c r="AF22" s="8">
         <v>397</v>
       </c>
-      <c r="AG22">
+      <c r="AG22" s="8">
         <v>493</v>
       </c>
-      <c r="AH22" s="1">
+      <c r="AH22" s="7">
         <v>1288</v>
       </c>
-      <c r="AI22">
+      <c r="AI22" s="8">
         <v>591</v>
       </c>
-      <c r="AJ22">
+      <c r="AJ22" s="8">
         <v>697</v>
       </c>
-      <c r="AK22" s="1">
+      <c r="AK22" s="7">
         <v>130</v>
       </c>
-      <c r="AL22">
+      <c r="AL22" s="8">
         <v>29</v>
       </c>
-      <c r="AM22">
+      <c r="AM22" s="8">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="8">
         <v>2023</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="8">
         <v>10</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="9">
         <v>4.75</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="7">
+        <f>'[1]לוח 1 table'!$M22</f>
         <v>2503</v>
       </c>
-      <c r="H23" s="1">
-        <v>3383</v>
-      </c>
-      <c r="I23" s="1">
-        <v>7222</v>
-      </c>
-      <c r="J23" s="1">
-        <v>870</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1023</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="H23" s="7">
+        <f>'[1]לוח 1 table'!$L22</f>
+        <v>3408</v>
+      </c>
+      <c r="I23" s="7">
+        <f>'[1]לוח 1 table'!$K22</f>
+        <v>7212</v>
+      </c>
+      <c r="J23" s="7">
+        <f>'[1]לוח 1 table'!$I22</f>
+        <v>867</v>
+      </c>
+      <c r="K23" s="7">
+        <f>'[1]לוח 1 table'!$H22</f>
+        <v>1035</v>
+      </c>
+      <c r="L23" s="7">
+        <f>'[1]לוח 1 table'!$G22</f>
         <v>2879</v>
       </c>
-      <c r="M23" s="1">
-        <v>1633</v>
-      </c>
-      <c r="N23" s="1">
-        <v>2360</v>
-      </c>
-      <c r="O23" s="1">
+      <c r="M23" s="7">
+        <f>'[1]לוח 1 table'!$D22</f>
+        <v>1636</v>
+      </c>
+      <c r="N23" s="7">
+        <f>'[1]לוח 1 table'!$C22</f>
+        <v>2373</v>
+      </c>
+      <c r="O23" s="7">
+        <f>'[1]לוח 1 table'!$B22</f>
+        <v>3700</v>
+      </c>
+      <c r="P23" s="7">
+        <f>'[2]2'!$E18</f>
+        <v>61581</v>
+      </c>
+      <c r="Q23" s="7">
+        <f>'[2]2'!$D18</f>
+        <v>62671</v>
+      </c>
+      <c r="R23" s="7">
+        <f>'[2]2'!$C18</f>
+        <v>62560</v>
+      </c>
+      <c r="S23" s="7">
+        <v>286</v>
+      </c>
+      <c r="T23" s="8">
+        <v>144</v>
+      </c>
+      <c r="U23" s="8">
+        <v>142</v>
+      </c>
+      <c r="V23" s="7">
+        <v>320</v>
+      </c>
+      <c r="W23" s="8">
+        <v>100</v>
+      </c>
+      <c r="X23" s="8">
+        <v>220</v>
+      </c>
+      <c r="Y23" s="7">
+        <v>490</v>
+      </c>
+      <c r="Z23" s="8">
+        <v>131</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>359</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>557</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>186</v>
+      </c>
+      <c r="AD23" s="8">
+        <v>371</v>
+      </c>
+      <c r="AE23" s="7">
+        <v>388</v>
+      </c>
+      <c r="AF23" s="8">
+        <v>155</v>
+      </c>
+      <c r="AG23" s="8">
+        <v>233</v>
+      </c>
+      <c r="AH23" s="7">
+        <v>383</v>
+      </c>
+      <c r="AI23" s="8">
+        <v>122</v>
+      </c>
+      <c r="AJ23" s="8">
+        <v>261</v>
+      </c>
+      <c r="AK23" s="7">
+        <v>82</v>
+      </c>
+      <c r="AL23" s="8">
+        <v>32</v>
+      </c>
+      <c r="AM23" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D24" s="8">
+        <v>11</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="9">
+        <v>4.75</v>
+      </c>
+      <c r="G24" s="7">
+        <f>'[1]לוח 1 table'!$M23</f>
+        <v>4535</v>
+      </c>
+      <c r="H24" s="7">
+        <f>'[1]לוח 1 table'!$L23</f>
+        <v>4400</v>
+      </c>
+      <c r="I24" s="7">
+        <f>'[1]לוח 1 table'!$K23</f>
+        <v>7491</v>
+      </c>
+      <c r="J24" s="7">
+        <f>'[1]לוח 1 table'!$I23</f>
+        <v>1553</v>
+      </c>
+      <c r="K24" s="7">
+        <f>'[1]לוח 1 table'!$H23</f>
+        <v>1506</v>
+      </c>
+      <c r="L24" s="7">
+        <f>'[1]לוח 1 table'!$G23</f>
+        <v>3044</v>
+      </c>
+      <c r="M24" s="7">
+        <f>'[1]לוח 1 table'!$D23</f>
+        <v>2982</v>
+      </c>
+      <c r="N24" s="7">
+        <f>'[1]לוח 1 table'!$C23</f>
+        <v>2893</v>
+      </c>
+      <c r="O24" s="7">
+        <f>'[1]לוח 1 table'!$B23</f>
+        <v>3835</v>
+      </c>
+      <c r="P24" s="7">
+        <f>'[2]2'!$E19</f>
+        <v>64002</v>
+      </c>
+      <c r="Q24" s="7">
+        <f>'[2]2'!$D19</f>
+        <v>63678</v>
+      </c>
+      <c r="R24" s="7">
+        <f>'[2]2'!$C19</f>
+        <v>63724</v>
+      </c>
+      <c r="S24" s="7">
+        <v>477</v>
+      </c>
+      <c r="T24" s="8">
+        <v>209</v>
+      </c>
+      <c r="U24" s="8">
+        <v>268</v>
+      </c>
+      <c r="V24" s="7">
+        <v>602</v>
+      </c>
+      <c r="W24" s="8">
+        <v>195</v>
+      </c>
+      <c r="X24" s="8">
+        <v>407</v>
+      </c>
+      <c r="Y24" s="7">
+        <v>708</v>
+      </c>
+      <c r="Z24" s="8">
+        <v>218</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>490</v>
+      </c>
+      <c r="AB24" s="7">
+        <v>1136</v>
+      </c>
+      <c r="AC24" s="8">
+        <v>361</v>
+      </c>
+      <c r="AD24" s="8">
+        <v>775</v>
+      </c>
+      <c r="AE24" s="7">
+        <v>730</v>
+      </c>
+      <c r="AF24" s="8">
+        <v>293</v>
+      </c>
+      <c r="AG24" s="8">
+        <v>437</v>
+      </c>
+      <c r="AH24" s="7">
+        <v>778</v>
+      </c>
+      <c r="AI24" s="8">
+        <v>251</v>
+      </c>
+      <c r="AJ24" s="8">
+        <v>527</v>
+      </c>
+      <c r="AK24" s="7">
+        <v>108</v>
+      </c>
+      <c r="AL24" s="8">
+        <v>28</v>
+      </c>
+      <c r="AM24" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D25" s="8">
+        <v>12</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="G25" s="7">
+        <f>'[1]לוח 1 table'!$M24</f>
+        <v>6566</v>
+      </c>
+      <c r="H25" s="7">
+        <f>'[1]לוח 1 table'!$L24</f>
+        <v>6331</v>
+      </c>
+      <c r="I25" s="7">
+        <f>'[1]לוח 1 table'!$K24</f>
+        <v>7756</v>
+      </c>
+      <c r="J25" s="7">
+        <f>'[1]לוח 1 table'!$I24</f>
+        <v>2859</v>
+      </c>
+      <c r="K25" s="7">
+        <f>'[1]לוח 1 table'!$H24</f>
+        <v>2524</v>
+      </c>
+      <c r="L25" s="7">
+        <f>'[1]לוח 1 table'!$G24</f>
+        <v>3236</v>
+      </c>
+      <c r="M25" s="7">
+        <f>'[1]לוח 1 table'!$D24</f>
         <v>3707</v>
       </c>
-      <c r="P23" s="1">
-        <v>61581</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>62619</v>
-      </c>
-      <c r="R23" s="1">
-        <v>62534</v>
-      </c>
-      <c r="S23" s="1">
-        <v>286</v>
-      </c>
-      <c r="T23">
-        <v>144</v>
-      </c>
-      <c r="U23">
+      <c r="N25" s="7">
+        <f>'[1]לוח 1 table'!$C24</f>
+        <v>3806</v>
+      </c>
+      <c r="O25" s="7">
+        <f>'[1]לוח 1 table'!$B24</f>
+        <v>4005</v>
+      </c>
+      <c r="P25" s="7">
+        <f>'[2]2'!$E20</f>
+        <v>68995</v>
+      </c>
+      <c r="Q25" s="7">
+        <f>'[2]2'!$D20</f>
+        <v>67512</v>
+      </c>
+      <c r="R25" s="7">
+        <f>'[2]2'!$C20</f>
+        <v>64763</v>
+      </c>
+      <c r="S25" s="7">
+        <v>663</v>
+      </c>
+      <c r="T25" s="8">
+        <v>340</v>
+      </c>
+      <c r="U25" s="8">
+        <v>323</v>
+      </c>
+      <c r="V25" s="7">
+        <v>668</v>
+      </c>
+      <c r="W25" s="8">
+        <v>271</v>
+      </c>
+      <c r="X25" s="8">
+        <v>397</v>
+      </c>
+      <c r="Y25" s="7">
+        <v>966</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>313</v>
+      </c>
+      <c r="AA25" s="8">
+        <v>653</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>1772</v>
+      </c>
+      <c r="AC25" s="8">
+        <v>795</v>
+      </c>
+      <c r="AD25" s="8">
+        <v>977</v>
+      </c>
+      <c r="AE25" s="7">
+        <v>1042</v>
+      </c>
+      <c r="AF25" s="8">
+        <v>513</v>
+      </c>
+      <c r="AG25" s="8">
+        <v>529</v>
+      </c>
+      <c r="AH25" s="7">
+        <v>1321</v>
+      </c>
+      <c r="AI25" s="8">
+        <v>589</v>
+      </c>
+      <c r="AJ25" s="8">
+        <v>732</v>
+      </c>
+      <c r="AK25" s="7">
         <v>142</v>
       </c>
-      <c r="V23" s="1">
-        <v>320</v>
-      </c>
-      <c r="W23">
-        <v>100</v>
-      </c>
-      <c r="X23">
-        <v>220</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>490</v>
-      </c>
-      <c r="Z23">
-        <v>131</v>
-      </c>
-      <c r="AA23">
-        <v>359</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>557</v>
-      </c>
-      <c r="AC23">
-        <v>186</v>
-      </c>
-      <c r="AD23">
-        <v>371</v>
-      </c>
-      <c r="AE23" s="1">
-        <v>388</v>
-      </c>
-      <c r="AF23">
-        <v>155</v>
-      </c>
-      <c r="AG23">
-        <v>233</v>
-      </c>
-      <c r="AH23" s="1">
-        <v>383</v>
-      </c>
-      <c r="AI23">
-        <v>122</v>
-      </c>
-      <c r="AJ23">
-        <v>261</v>
-      </c>
-      <c r="AK23" s="1">
-        <v>82</v>
-      </c>
-      <c r="AL23">
-        <v>32</v>
-      </c>
-      <c r="AM23">
-        <v>50</v>
+      <c r="AL25" s="8">
+        <v>40</v>
+      </c>
+      <c r="AM25" s="8">
+        <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24">
-        <v>2023</v>
-      </c>
-      <c r="D24">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" s="3">
-        <v>4.75</v>
-      </c>
-      <c r="G24" s="1">
-        <v>4540</v>
-      </c>
-      <c r="H24" s="1">
-        <v>4428</v>
-      </c>
-      <c r="I24" s="1">
-        <v>7507</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1555</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1521</v>
-      </c>
-      <c r="L24" s="1">
-        <v>3044</v>
-      </c>
-      <c r="M24" s="1">
-        <v>2985</v>
-      </c>
-      <c r="N24" s="1">
-        <v>2907</v>
-      </c>
-      <c r="O24" s="1">
-        <v>3843</v>
-      </c>
-      <c r="P24" s="1">
-        <v>64002</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>63676</v>
-      </c>
-      <c r="R24" s="1">
-        <v>63695</v>
-      </c>
-      <c r="S24" s="1">
-        <v>477</v>
-      </c>
-      <c r="T24">
-        <v>209</v>
-      </c>
-      <c r="U24">
-        <v>268</v>
-      </c>
-      <c r="V24" s="1">
-        <v>602</v>
-      </c>
-      <c r="W24">
-        <v>195</v>
-      </c>
-      <c r="X24">
-        <v>407</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>708</v>
-      </c>
-      <c r="Z24">
-        <v>218</v>
-      </c>
-      <c r="AA24">
-        <v>490</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>1136</v>
-      </c>
-      <c r="AC24">
-        <v>361</v>
-      </c>
-      <c r="AD24">
-        <v>775</v>
-      </c>
-      <c r="AE24" s="1">
-        <v>730</v>
-      </c>
-      <c r="AF24">
-        <v>293</v>
-      </c>
-      <c r="AG24">
-        <v>437</v>
-      </c>
-      <c r="AH24" s="1">
-        <v>778</v>
-      </c>
-      <c r="AI24">
-        <v>251</v>
-      </c>
-      <c r="AJ24">
-        <v>527</v>
-      </c>
-      <c r="AK24" s="1">
-        <v>108</v>
-      </c>
-      <c r="AL24">
-        <v>28</v>
-      </c>
-      <c r="AM24">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25">
-        <v>2023</v>
-      </c>
-      <c r="D25">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="3">
+    <row r="26" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="9">
         <v>4.5</v>
       </c>
-      <c r="G25" s="1">
-        <v>6575</v>
-      </c>
-      <c r="H25" s="1">
-        <v>6336</v>
-      </c>
-      <c r="I25" s="1">
-        <v>7775</v>
-      </c>
-      <c r="J25" s="1">
-        <v>2861</v>
-      </c>
-      <c r="K25" s="1">
-        <v>2519</v>
-      </c>
-      <c r="L25" s="1">
-        <v>3234</v>
-      </c>
-      <c r="M25" s="1">
-        <v>3714</v>
-      </c>
-      <c r="N25" s="1">
-        <v>3818</v>
-      </c>
-      <c r="O25" s="1">
-        <v>4011</v>
-      </c>
-      <c r="P25" s="1">
-        <v>68995</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>67561</v>
-      </c>
-      <c r="R25" s="1">
-        <v>64741</v>
-      </c>
-      <c r="S25" s="1">
-        <v>663</v>
-      </c>
-      <c r="T25">
-        <v>340</v>
-      </c>
-      <c r="U25">
-        <v>323</v>
-      </c>
-      <c r="V25" s="1">
-        <v>668</v>
-      </c>
-      <c r="W25">
-        <v>271</v>
-      </c>
-      <c r="X25">
-        <v>397</v>
-      </c>
-      <c r="Y25" s="1">
-        <v>966</v>
-      </c>
-      <c r="Z25">
-        <v>313</v>
-      </c>
-      <c r="AA25">
-        <v>653</v>
-      </c>
-      <c r="AB25" s="1">
-        <v>1772</v>
-      </c>
-      <c r="AC25">
-        <v>795</v>
-      </c>
-      <c r="AD25">
-        <v>977</v>
-      </c>
-      <c r="AE25" s="1">
-        <v>1042</v>
-      </c>
-      <c r="AF25">
-        <v>513</v>
-      </c>
-      <c r="AG25">
-        <v>529</v>
-      </c>
-      <c r="AH25" s="1">
-        <v>1321</v>
-      </c>
-      <c r="AI25">
-        <v>589</v>
-      </c>
-      <c r="AJ25">
-        <v>732</v>
-      </c>
-      <c r="AK25" s="1">
-        <v>142</v>
-      </c>
-      <c r="AL25">
-        <v>40</v>
-      </c>
-      <c r="AM25">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26">
-        <v>2024</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="G26" s="1">
-        <v>8785</v>
-      </c>
-      <c r="H26" s="1">
-        <v>8277</v>
-      </c>
-      <c r="I26" s="1">
-        <v>8024</v>
-      </c>
-      <c r="J26" s="1">
-        <v>3961</v>
-      </c>
-      <c r="K26" s="1">
-        <v>3803</v>
-      </c>
-      <c r="L26" s="1">
-        <v>3433</v>
-      </c>
-      <c r="M26" s="1">
-        <v>4824</v>
-      </c>
-      <c r="N26" s="1">
-        <v>4474</v>
-      </c>
-      <c r="O26" s="1">
-        <v>4193</v>
-      </c>
-      <c r="P26" s="1">
+      <c r="G26" s="7">
+        <f>'[1]לוח 1 table'!$M25</f>
+        <v>8783</v>
+      </c>
+      <c r="H26" s="7">
+        <f>'[1]לוח 1 table'!$L25</f>
+        <v>8282</v>
+      </c>
+      <c r="I26" s="7">
+        <f>'[1]לוח 1 table'!$K25</f>
+        <v>8005</v>
+      </c>
+      <c r="J26" s="7">
+        <f>'[1]לוח 1 table'!$I25</f>
+        <v>3958</v>
+      </c>
+      <c r="K26" s="7">
+        <f>'[1]לוח 1 table'!$H25</f>
+        <v>3810</v>
+      </c>
+      <c r="L26" s="7">
+        <f>'[1]לוח 1 table'!$G25</f>
+        <v>3440</v>
+      </c>
+      <c r="M26" s="7">
+        <f>'[1]לוח 1 table'!$D25</f>
+        <v>4825</v>
+      </c>
+      <c r="N26" s="7">
+        <f>'[1]לוח 1 table'!$C25</f>
+        <v>4471</v>
+      </c>
+      <c r="O26" s="7">
+        <f>'[1]לוח 1 table'!$B25</f>
+        <v>4191</v>
+      </c>
+      <c r="P26" s="7">
+        <f>'[2]2'!$E21</f>
         <v>68632</v>
       </c>
-      <c r="Q26" s="1">
-        <v>66141</v>
-      </c>
-      <c r="R26" s="1">
-        <v>65642</v>
-      </c>
-      <c r="S26" s="1">
+      <c r="Q26" s="7">
+        <f>'[2]2'!$D21</f>
+        <v>66161</v>
+      </c>
+      <c r="R26" s="7">
+        <f>'[2]2'!$C21</f>
+        <v>65649</v>
+      </c>
+      <c r="S26" s="7">
+        <f>T26+U26</f>
         <v>763</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="8">
+        <f>'[3]לוח 3 table'!$G36</f>
         <v>337</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="8">
+        <f>'[3]לוח 3 table'!$G90</f>
         <v>426</v>
       </c>
-      <c r="V26" s="1">
+      <c r="V26" s="7">
+        <f>W26+X26</f>
         <v>953</v>
       </c>
-      <c r="W26">
-        <v>388</v>
-      </c>
-      <c r="X26">
-        <v>565</v>
-      </c>
-      <c r="Y26" s="1">
+      <c r="W26" s="8">
+        <f>'[3]לוח 3 table'!$F36</f>
+        <v>387</v>
+      </c>
+      <c r="X26" s="8">
+        <f>'[3]לוח 3 table'!$F90</f>
+        <v>566</v>
+      </c>
+      <c r="Y26" s="7">
+        <f>Z26+AA26</f>
         <v>1300</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="8">
+        <f>'[3]לוח 3 table'!$E36</f>
         <v>398</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="8">
+        <f>'[3]לוח 3 table'!$E90</f>
         <v>902</v>
       </c>
-      <c r="AB26" s="1">
-        <v>2370</v>
-      </c>
-      <c r="AC26">
-        <v>1222</v>
-      </c>
-      <c r="AD26">
+      <c r="AB26" s="7">
+        <f>AC26+AD26</f>
+        <v>2369</v>
+      </c>
+      <c r="AC26" s="8">
+        <f>'[3]לוח 3 table'!$D36</f>
+        <v>1221</v>
+      </c>
+      <c r="AD26" s="8">
+        <f>'[3]לוח 3 table'!$D90</f>
         <v>1148</v>
       </c>
-      <c r="AE26" s="1">
-        <v>1289</v>
-      </c>
-      <c r="AF26">
-        <v>613</v>
-      </c>
-      <c r="AG26">
+      <c r="AE26" s="7">
+        <f>AF26+AG26</f>
+        <v>1290</v>
+      </c>
+      <c r="AF26" s="8">
+        <f>'[3]לוח 3 table'!$C36</f>
+        <v>614</v>
+      </c>
+      <c r="AG26" s="8">
+        <f>'[3]לוח 3 table'!$C90</f>
         <v>676</v>
       </c>
-      <c r="AH26" s="1">
-        <v>1881</v>
-      </c>
-      <c r="AI26">
-        <v>934</v>
-      </c>
-      <c r="AJ26">
+      <c r="AH26" s="7">
+        <f>AI26+AJ26</f>
+        <v>1879</v>
+      </c>
+      <c r="AI26" s="8">
+        <f>'[3]לוח 3 table'!$B36</f>
+        <v>932</v>
+      </c>
+      <c r="AJ26" s="8">
+        <f>'[3]לוח 3 table'!$B90</f>
         <v>947</v>
       </c>
-      <c r="AK26" s="1">
+      <c r="AK26" s="7">
+        <f>AL26+AM26</f>
         <v>228</v>
       </c>
-      <c r="AL26">
+      <c r="AL26" s="8">
+        <f>'[3]לוח 3 table'!$A36</f>
         <v>69</v>
       </c>
-      <c r="AM26">
+      <c r="AM26" s="8">
+        <f>'[3]לוח 3 table'!$A90</f>
         <v>159</v>
       </c>
     </row>
@@ -3809,102 +5907,135 @@
         <v>4.5</v>
       </c>
       <c r="G27" s="1">
-        <v>8389</v>
+        <f>'[1]לוח 1 table'!$M26</f>
+        <v>8395</v>
       </c>
       <c r="H27" s="1">
-        <v>8217</v>
+        <f>'[1]לוח 1 table'!$L26</f>
+        <v>8202</v>
       </c>
       <c r="I27" s="1">
-        <v>8253</v>
+        <f>'[1]לוח 1 table'!$K26</f>
+        <v>8239</v>
       </c>
       <c r="J27" s="1">
-        <v>3802</v>
+        <f>'[1]לוח 1 table'!$I26</f>
+        <v>3795</v>
       </c>
       <c r="K27" s="1">
-        <v>3712</v>
+        <f>'[1]לוח 1 table'!$H26</f>
+        <v>3684</v>
       </c>
       <c r="L27" s="1">
-        <v>3616</v>
+        <f>'[1]לוח 1 table'!$G26</f>
+        <v>3627</v>
       </c>
       <c r="M27" s="1">
-        <v>4587</v>
+        <f>'[1]לוח 1 table'!$D26</f>
+        <v>4600</v>
       </c>
       <c r="N27" s="1">
-        <v>4504</v>
+        <f>'[1]לוח 1 table'!$C26</f>
+        <v>4518</v>
       </c>
       <c r="O27" s="1">
-        <v>4375</v>
-      </c>
-      <c r="P27" s="1">
+        <f>'[1]לוח 1 table'!$B26</f>
+        <v>4377</v>
+      </c>
+      <c r="P27" s="7">
+        <f>'[2]2'!$E22</f>
         <v>67910</v>
       </c>
-      <c r="Q27" s="1">
-        <v>65994</v>
-      </c>
-      <c r="R27" s="1">
-        <v>66388</v>
-      </c>
-      <c r="S27" s="1">
-        <v>734</v>
-      </c>
-      <c r="T27">
-        <v>301</v>
-      </c>
-      <c r="U27">
+      <c r="Q27" s="7">
+        <f>'[2]2'!$D22</f>
+        <v>66074</v>
+      </c>
+      <c r="R27" s="7">
+        <f>'[2]2'!$C22</f>
+        <v>66380</v>
+      </c>
+      <c r="S27" s="7">
+        <f t="shared" ref="S27:S41" si="0">T27+U27</f>
+        <v>732</v>
+      </c>
+      <c r="T27" s="8">
+        <f>'[3]לוח 3 table'!$G37</f>
+        <v>299</v>
+      </c>
+      <c r="U27" s="8">
+        <f>'[3]לוח 3 table'!$G91</f>
         <v>433</v>
       </c>
-      <c r="V27" s="1">
-        <v>860</v>
-      </c>
-      <c r="W27">
-        <v>356</v>
-      </c>
-      <c r="X27">
+      <c r="V27" s="7">
+        <f t="shared" ref="V27:V41" si="1">W27+X27</f>
+        <v>859</v>
+      </c>
+      <c r="W27" s="8">
+        <f>'[3]לוח 3 table'!$F37</f>
+        <v>355</v>
+      </c>
+      <c r="X27" s="8">
+        <f>'[3]לוח 3 table'!$F91</f>
         <v>504</v>
       </c>
-      <c r="Y27" s="1">
-        <v>1333</v>
-      </c>
-      <c r="Z27">
+      <c r="Y27" s="7">
+        <f t="shared" ref="Y27:Y41" si="2">Z27+AA27</f>
+        <v>1330</v>
+      </c>
+      <c r="Z27" s="8">
+        <f>'[3]לוח 3 table'!$E37</f>
         <v>513</v>
       </c>
-      <c r="AA27">
-        <v>820</v>
-      </c>
-      <c r="AB27" s="1">
-        <v>2207</v>
-      </c>
-      <c r="AC27">
+      <c r="AA27" s="8">
+        <f>'[3]לוח 3 table'!$E91</f>
+        <v>817</v>
+      </c>
+      <c r="AB27" s="7">
+        <f t="shared" ref="AB27:AB41" si="3">AC27+AD27</f>
+        <v>2223</v>
+      </c>
+      <c r="AC27" s="8">
+        <f>'[3]לוח 3 table'!$D37</f>
         <v>1164</v>
       </c>
-      <c r="AD27">
-        <v>1043</v>
-      </c>
-      <c r="AE27" s="1">
-        <v>1344</v>
-      </c>
-      <c r="AF27">
-        <v>630</v>
-      </c>
-      <c r="AG27">
+      <c r="AD27" s="8">
+        <f>'[3]לוח 3 table'!$D91</f>
+        <v>1059</v>
+      </c>
+      <c r="AE27" s="7">
+        <f t="shared" ref="AE27:AE41" si="4">AF27+AG27</f>
+        <v>1343</v>
+      </c>
+      <c r="AF27" s="8">
+        <f>'[3]לוח 3 table'!$C37</f>
+        <v>629</v>
+      </c>
+      <c r="AG27" s="8">
+        <f>'[3]לוח 3 table'!$C91</f>
         <v>714</v>
       </c>
-      <c r="AH27" s="1">
-        <v>1695</v>
-      </c>
-      <c r="AI27">
-        <v>790</v>
-      </c>
-      <c r="AJ27">
+      <c r="AH27" s="7">
+        <f t="shared" ref="AH27:AH41" si="5">AI27+AJ27</f>
+        <v>1694</v>
+      </c>
+      <c r="AI27" s="8">
+        <f>'[3]לוח 3 table'!$B37</f>
+        <v>789</v>
+      </c>
+      <c r="AJ27" s="8">
+        <f>'[3]לוח 3 table'!$B91</f>
         <v>905</v>
       </c>
-      <c r="AK27" s="1">
-        <v>216</v>
-      </c>
-      <c r="AL27">
-        <v>48</v>
-      </c>
-      <c r="AM27">
+      <c r="AK27" s="7">
+        <f t="shared" ref="AK27:AK41" si="6">AL27+AM27</f>
+        <v>214</v>
+      </c>
+      <c r="AL27" s="8">
+        <f>'[3]לוח 3 table'!$A37</f>
+        <v>46</v>
+      </c>
+      <c r="AM27" s="8">
+        <f>'[3]לוח 3 table'!$A91</f>
         <v>168</v>
       </c>
     </row>
@@ -3928,102 +6059,135 @@
         <v>4.5</v>
       </c>
       <c r="G28" s="1">
-        <v>8756</v>
+        <f>'[1]לוח 1 table'!$M27</f>
+        <v>8751</v>
       </c>
       <c r="H28" s="1">
-        <v>8511</v>
+        <f>'[1]לוח 1 table'!$L27</f>
+        <v>8440</v>
       </c>
       <c r="I28" s="1">
-        <v>8453</v>
+        <f>'[1]לוח 1 table'!$K27</f>
+        <v>8447</v>
       </c>
       <c r="J28" s="1">
-        <v>3961</v>
+        <f>'[1]לוח 1 table'!$I27</f>
+        <v>3957</v>
       </c>
       <c r="K28" s="1">
-        <v>3876</v>
+        <f>'[1]לוח 1 table'!$H27</f>
+        <v>3826</v>
       </c>
       <c r="L28" s="1">
-        <v>3763</v>
+        <f>'[1]לוח 1 table'!$G27</f>
+        <v>3775</v>
       </c>
       <c r="M28" s="1">
-        <v>4795</v>
+        <f>'[1]לוח 1 table'!$D27</f>
+        <v>4794</v>
       </c>
       <c r="N28" s="1">
-        <v>4635</v>
+        <f>'[1]לוח 1 table'!$C27</f>
+        <v>4614</v>
       </c>
       <c r="O28" s="1">
-        <v>4546</v>
-      </c>
-      <c r="P28" s="1">
+        <f>'[1]לוח 1 table'!$B27</f>
+        <v>4550</v>
+      </c>
+      <c r="P28" s="7">
+        <f>'[2]2'!$E23</f>
         <v>67015</v>
       </c>
-      <c r="Q28" s="1">
-        <v>67506</v>
-      </c>
-      <c r="R28" s="1">
-        <v>66992</v>
-      </c>
-      <c r="S28" s="1">
-        <v>713</v>
-      </c>
-      <c r="T28">
+      <c r="Q28" s="7">
+        <f>'[2]2'!$D23</f>
+        <v>67490</v>
+      </c>
+      <c r="R28" s="7">
+        <f>'[2]2'!$C23</f>
+        <v>66971</v>
+      </c>
+      <c r="S28" s="7">
+        <f t="shared" si="0"/>
+        <v>714</v>
+      </c>
+      <c r="T28" s="8">
+        <f>'[3]לוח 3 table'!$G38</f>
         <v>272</v>
       </c>
-      <c r="U28">
-        <v>441</v>
-      </c>
-      <c r="V28" s="1">
-        <v>893</v>
-      </c>
-      <c r="W28">
-        <v>363</v>
-      </c>
-      <c r="X28">
-        <v>530</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>1369</v>
-      </c>
-      <c r="Z28">
+      <c r="U28" s="8">
+        <f>'[3]לוח 3 table'!$G92</f>
+        <v>442</v>
+      </c>
+      <c r="V28" s="7">
+        <f t="shared" si="1"/>
+        <v>891</v>
+      </c>
+      <c r="W28" s="8">
+        <f>'[3]לוח 3 table'!$F38</f>
+        <v>362</v>
+      </c>
+      <c r="X28" s="8">
+        <f>'[3]לוח 3 table'!$F92</f>
+        <v>529</v>
+      </c>
+      <c r="Y28" s="7">
+        <f t="shared" si="2"/>
+        <v>1368</v>
+      </c>
+      <c r="Z28" s="8">
+        <f>'[3]לוח 3 table'!$E38</f>
         <v>467</v>
       </c>
-      <c r="AA28">
-        <v>902</v>
-      </c>
-      <c r="AB28" s="1">
-        <v>2362</v>
-      </c>
-      <c r="AC28">
-        <v>1236</v>
-      </c>
-      <c r="AD28">
+      <c r="AA28" s="8">
+        <f>'[3]לוח 3 table'!$E92</f>
+        <v>901</v>
+      </c>
+      <c r="AB28" s="7">
+        <f t="shared" si="3"/>
+        <v>2360</v>
+      </c>
+      <c r="AC28" s="8">
+        <f>'[3]לוח 3 table'!$D38</f>
+        <v>1234</v>
+      </c>
+      <c r="AD28" s="8">
+        <f>'[3]לוח 3 table'!$D92</f>
         <v>1126</v>
       </c>
-      <c r="AE28" s="1">
+      <c r="AE28" s="7">
+        <f t="shared" si="4"/>
         <v>1469</v>
       </c>
-      <c r="AF28">
+      <c r="AF28" s="8">
+        <f>'[3]לוח 3 table'!$C38</f>
         <v>736</v>
       </c>
-      <c r="AG28">
+      <c r="AG28" s="8">
+        <f>'[3]לוח 3 table'!$C92</f>
         <v>733</v>
       </c>
-      <c r="AH28" s="1">
+      <c r="AH28" s="7">
+        <f t="shared" si="5"/>
         <v>1771</v>
       </c>
-      <c r="AI28">
+      <c r="AI28" s="8">
+        <f>'[3]לוח 3 table'!$B38</f>
         <v>856</v>
       </c>
-      <c r="AJ28">
+      <c r="AJ28" s="8">
+        <f>'[3]לוח 3 table'!$B92</f>
         <v>915</v>
       </c>
-      <c r="AK28" s="1">
-        <v>178</v>
-      </c>
-      <c r="AL28">
-        <v>31</v>
-      </c>
-      <c r="AM28">
+      <c r="AK28" s="7">
+        <f t="shared" si="6"/>
+        <v>177</v>
+      </c>
+      <c r="AL28" s="8">
+        <f>'[3]לוח 3 table'!$A38</f>
+        <v>30</v>
+      </c>
+      <c r="AM28" s="8">
+        <f>'[3]לוח 3 table'!$A92</f>
         <v>147</v>
       </c>
     </row>
@@ -4047,102 +6211,135 @@
         <v>4.5</v>
       </c>
       <c r="G29" s="1">
+        <f>'[1]לוח 1 table'!$M28</f>
         <v>7833</v>
       </c>
       <c r="H29" s="1">
-        <v>8546</v>
+        <f>'[1]לוח 1 table'!$L28</f>
+        <v>8602</v>
       </c>
       <c r="I29" s="1">
-        <v>8605</v>
+        <f>'[1]לוח 1 table'!$K28</f>
+        <v>8608</v>
       </c>
       <c r="J29" s="1">
-        <v>3506</v>
+        <f>'[1]לוח 1 table'!$I28</f>
+        <v>3505</v>
       </c>
       <c r="K29" s="1">
-        <v>3874</v>
+        <f>'[1]לוח 1 table'!$H28</f>
+        <v>3916</v>
       </c>
       <c r="L29" s="1">
-        <v>3857</v>
+        <f>'[1]לוח 1 table'!$G28</f>
+        <v>3866</v>
       </c>
       <c r="M29" s="1">
-        <v>4327</v>
+        <f>'[1]לוח 1 table'!$D28</f>
+        <v>4328</v>
       </c>
       <c r="N29" s="1">
-        <v>4671</v>
+        <f>'[1]לוח 1 table'!$C28</f>
+        <v>4686</v>
       </c>
       <c r="O29" s="1">
-        <v>4699</v>
-      </c>
-      <c r="P29" s="1">
+        <f>'[1]לוח 1 table'!$B28</f>
+        <v>4705</v>
+      </c>
+      <c r="P29" s="7">
+        <f>'[2]2'!$E24</f>
         <v>65876</v>
       </c>
-      <c r="Q29" s="1">
-        <v>67520</v>
-      </c>
-      <c r="R29" s="1">
-        <v>67478</v>
-      </c>
-      <c r="S29" s="1">
-        <v>725</v>
-      </c>
-      <c r="T29">
-        <v>318</v>
-      </c>
-      <c r="U29">
-        <v>407</v>
-      </c>
-      <c r="V29" s="1">
+      <c r="Q29" s="7">
+        <f>'[2]2'!$D24</f>
+        <v>67448</v>
+      </c>
+      <c r="R29" s="7">
+        <f>'[2]2'!$C24</f>
+        <v>67452</v>
+      </c>
+      <c r="S29" s="7">
+        <f t="shared" si="0"/>
+        <v>722</v>
+      </c>
+      <c r="T29" s="8">
+        <f>'[3]לוח 3 table'!$G39</f>
+        <v>316</v>
+      </c>
+      <c r="U29" s="8">
+        <f>'[3]לוח 3 table'!$G93</f>
+        <v>406</v>
+      </c>
+      <c r="V29" s="7">
+        <f t="shared" si="1"/>
         <v>891</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="8">
+        <f>'[3]לוח 3 table'!$F39</f>
         <v>460</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="8">
+        <f>'[3]לוח 3 table'!$F93</f>
         <v>431</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Y29" s="7">
+        <f t="shared" si="2"/>
         <v>1222</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="8">
+        <f>'[3]לוח 3 table'!$E39</f>
         <v>459</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="8">
+        <f>'[3]לוח 3 table'!$E93</f>
         <v>763</v>
       </c>
-      <c r="AB29" s="1">
-        <v>1959</v>
-      </c>
-      <c r="AC29">
-        <v>860</v>
-      </c>
-      <c r="AD29">
-        <v>1099</v>
-      </c>
-      <c r="AE29" s="1">
-        <v>1386</v>
-      </c>
-      <c r="AF29">
-        <v>702</v>
-      </c>
-      <c r="AG29">
+      <c r="AB29" s="7">
+        <f t="shared" si="3"/>
+        <v>1960</v>
+      </c>
+      <c r="AC29" s="8">
+        <f>'[3]לוח 3 table'!$D39</f>
+        <v>859</v>
+      </c>
+      <c r="AD29" s="8">
+        <f>'[3]לוח 3 table'!$D93</f>
+        <v>1101</v>
+      </c>
+      <c r="AE29" s="7">
+        <f t="shared" si="4"/>
+        <v>1388</v>
+      </c>
+      <c r="AF29" s="8">
+        <f>'[3]לוח 3 table'!$C39</f>
+        <v>703</v>
+      </c>
+      <c r="AG29" s="8">
+        <f>'[3]לוח 3 table'!$C93</f>
+        <v>685</v>
+      </c>
+      <c r="AH29" s="7">
+        <f t="shared" si="5"/>
+        <v>1523</v>
+      </c>
+      <c r="AI29" s="8">
+        <f>'[3]לוח 3 table'!$B39</f>
         <v>684</v>
       </c>
-      <c r="AH29" s="1">
-        <v>1523</v>
-      </c>
-      <c r="AI29">
-        <v>683</v>
-      </c>
-      <c r="AJ29">
-        <v>840</v>
-      </c>
-      <c r="AK29" s="1">
+      <c r="AJ29" s="8">
+        <f>'[3]לוח 3 table'!$B93</f>
+        <v>839</v>
+      </c>
+      <c r="AK29" s="7">
+        <f t="shared" si="6"/>
         <v>128</v>
       </c>
-      <c r="AL29">
+      <c r="AL29" s="8">
+        <f>'[3]לוח 3 table'!$A39</f>
         <v>25</v>
       </c>
-      <c r="AM29">
+      <c r="AM29" s="8">
+        <f>'[3]לוח 3 table'!$A93</f>
         <v>103</v>
       </c>
     </row>
@@ -4166,102 +6363,135 @@
         <v>4.5</v>
       </c>
       <c r="G30" s="1">
-        <v>8476</v>
+        <f>'[1]לוח 1 table'!$M29</f>
+        <v>8472</v>
       </c>
       <c r="H30" s="1">
-        <v>8478</v>
+        <f>'[1]לוח 1 table'!$L29</f>
+        <v>8475</v>
       </c>
       <c r="I30" s="1">
-        <v>8685</v>
+        <f>'[1]לוח 1 table'!$K29</f>
+        <v>8697</v>
       </c>
       <c r="J30" s="1">
-        <v>3928</v>
+        <f>'[1]לוח 1 table'!$I29</f>
+        <v>3923</v>
       </c>
       <c r="K30" s="1">
-        <v>3877</v>
+        <f>'[1]לוח 1 table'!$H29</f>
+        <v>3860</v>
       </c>
       <c r="L30" s="1">
-        <v>3888</v>
+        <f>'[1]לוח 1 table'!$G29</f>
+        <v>3893</v>
       </c>
       <c r="M30" s="1">
-        <v>4548</v>
+        <f>'[1]לוח 1 table'!$D29</f>
+        <v>4549</v>
       </c>
       <c r="N30" s="1">
-        <v>4601</v>
+        <f>'[1]לוח 1 table'!$C29</f>
+        <v>4614</v>
       </c>
       <c r="O30" s="1">
-        <v>4838</v>
-      </c>
-      <c r="P30" s="1">
+        <f>'[1]לוח 1 table'!$B29</f>
+        <v>4844</v>
+      </c>
+      <c r="P30" s="7">
+        <f>'[2]2'!$E25</f>
         <v>66841</v>
       </c>
-      <c r="Q30" s="1">
-        <v>67818</v>
-      </c>
-      <c r="R30" s="1">
-        <v>67884</v>
-      </c>
-      <c r="S30" s="1">
-        <v>737</v>
-      </c>
-      <c r="T30">
-        <v>364</v>
-      </c>
-      <c r="U30">
+      <c r="Q30" s="7">
+        <f>'[2]2'!$D25</f>
+        <v>67768</v>
+      </c>
+      <c r="R30" s="7">
+        <f>'[2]2'!$C25</f>
+        <v>67869</v>
+      </c>
+      <c r="S30" s="7">
+        <f t="shared" si="0"/>
+        <v>738</v>
+      </c>
+      <c r="T30" s="8">
+        <f>'[3]לוח 3 table'!$G40</f>
+        <v>365</v>
+      </c>
+      <c r="U30" s="8">
+        <f>'[3]לוח 3 table'!$G94</f>
         <v>373</v>
       </c>
-      <c r="V30" s="1">
+      <c r="V30" s="7">
+        <f t="shared" si="1"/>
         <v>1018</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="8">
+        <f>'[3]לוח 3 table'!$F40</f>
         <v>494</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="8">
+        <f>'[3]לוח 3 table'!$F94</f>
         <v>524</v>
       </c>
-      <c r="Y30" s="1">
-        <v>1344</v>
-      </c>
-      <c r="Z30">
-        <v>529</v>
-      </c>
-      <c r="AA30">
+      <c r="Y30" s="7">
+        <f t="shared" si="2"/>
+        <v>1338</v>
+      </c>
+      <c r="Z30" s="8">
+        <f>'[3]לוח 3 table'!$E40</f>
+        <v>523</v>
+      </c>
+      <c r="AA30" s="8">
+        <f>'[3]לוח 3 table'!$E94</f>
         <v>815</v>
       </c>
-      <c r="AB30" s="1">
-        <v>2102</v>
-      </c>
-      <c r="AC30">
-        <v>971</v>
-      </c>
-      <c r="AD30">
+      <c r="AB30" s="7">
+        <f t="shared" si="3"/>
+        <v>2101</v>
+      </c>
+      <c r="AC30" s="8">
+        <f>'[3]לוח 3 table'!$D40</f>
+        <v>970</v>
+      </c>
+      <c r="AD30" s="8">
+        <f>'[3]לוח 3 table'!$D94</f>
         <v>1131</v>
       </c>
-      <c r="AE30" s="1">
-        <v>1440</v>
-      </c>
-      <c r="AF30">
-        <v>793</v>
-      </c>
-      <c r="AG30">
-        <v>647</v>
-      </c>
-      <c r="AH30" s="1">
+      <c r="AE30" s="7">
+        <f t="shared" si="4"/>
+        <v>1442</v>
+      </c>
+      <c r="AF30" s="8">
+        <f>'[3]לוח 3 table'!$C40</f>
+        <v>794</v>
+      </c>
+      <c r="AG30" s="8">
+        <f>'[3]לוח 3 table'!$C94</f>
+        <v>648</v>
+      </c>
+      <c r="AH30" s="7">
+        <f t="shared" si="5"/>
         <v>1634</v>
       </c>
-      <c r="AI30">
+      <c r="AI30" s="8">
+        <f>'[3]לוח 3 table'!$B40</f>
         <v>738</v>
       </c>
-      <c r="AJ30">
+      <c r="AJ30" s="8">
+        <f>'[3]לוח 3 table'!$B94</f>
         <v>896</v>
       </c>
-      <c r="AK30" s="1">
+      <c r="AK30" s="7">
+        <f t="shared" si="6"/>
         <v>199</v>
       </c>
-      <c r="AL30">
+      <c r="AL30" s="8">
+        <f>'[3]לוח 3 table'!$A40</f>
         <v>37</v>
       </c>
-      <c r="AM30">
+      <c r="AM30" s="8">
+        <f>'[3]לוח 3 table'!$A94</f>
         <v>162</v>
       </c>
     </row>
@@ -4285,102 +6515,135 @@
         <v>4.5</v>
       </c>
       <c r="G31" s="1">
-        <v>8808</v>
+        <f>'[1]לוח 1 table'!$M30</f>
+        <v>8810</v>
       </c>
       <c r="H31" s="1">
-        <v>8832</v>
+        <f>'[1]לוח 1 table'!$L30</f>
+        <v>8838</v>
       </c>
       <c r="I31" s="1">
-        <v>8677</v>
+        <f>'[1]לוח 1 table'!$K30</f>
+        <v>8696</v>
       </c>
       <c r="J31" s="1">
-        <v>3786</v>
+        <f>'[1]לוח 1 table'!$I30</f>
+        <v>3787</v>
       </c>
       <c r="K31" s="1">
-        <v>3866</v>
+        <f>'[1]לוח 1 table'!$H30</f>
+        <v>3859</v>
       </c>
       <c r="L31" s="1">
-        <v>3857</v>
+        <f>'[1]לוח 1 table'!$G30</f>
+        <v>3862</v>
       </c>
       <c r="M31" s="1">
-        <v>5022</v>
+        <f>'[1]לוח 1 table'!$D30</f>
+        <v>5023</v>
       </c>
       <c r="N31" s="1">
-        <v>4966</v>
+        <f>'[1]לוח 1 table'!$C30</f>
+        <v>4978</v>
       </c>
       <c r="O31" s="1">
-        <v>4969</v>
-      </c>
-      <c r="P31" s="1">
+        <f>'[1]לוח 1 table'!$B30</f>
+        <v>4978</v>
+      </c>
+      <c r="P31" s="7">
+        <f>'[2]2'!$E26</f>
         <v>67619</v>
       </c>
-      <c r="Q31" s="1">
-        <v>68659</v>
-      </c>
-      <c r="R31" s="1">
-        <v>68268</v>
-      </c>
-      <c r="S31" s="1">
+      <c r="Q31" s="7">
+        <f>'[2]2'!$D26</f>
+        <v>68610</v>
+      </c>
+      <c r="R31" s="7">
+        <f>'[2]2'!$C26</f>
+        <v>68270</v>
+      </c>
+      <c r="S31" s="7">
+        <f t="shared" si="0"/>
         <v>749</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="8">
+        <f>'[3]לוח 3 table'!$G41</f>
         <v>295</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="8">
+        <f>'[3]לוח 3 table'!$G95</f>
         <v>454</v>
       </c>
-      <c r="V31" s="1">
-        <v>1061</v>
-      </c>
-      <c r="W31">
+      <c r="V31" s="7">
+        <f t="shared" si="1"/>
+        <v>1062</v>
+      </c>
+      <c r="W31" s="8">
+        <f>'[3]לוח 3 table'!$F41</f>
         <v>442</v>
       </c>
-      <c r="X31">
-        <v>619</v>
-      </c>
-      <c r="Y31" s="1">
+      <c r="X31" s="8">
+        <f>'[3]לוח 3 table'!$F95</f>
+        <v>620</v>
+      </c>
+      <c r="Y31" s="7">
+        <f t="shared" si="2"/>
         <v>1280</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="8">
+        <f>'[3]לוח 3 table'!$E41</f>
         <v>391</v>
       </c>
-      <c r="AA31">
+      <c r="AA31" s="8">
+        <f>'[3]לוח 3 table'!$E95</f>
         <v>889</v>
       </c>
-      <c r="AB31" s="1">
-        <v>2027</v>
-      </c>
-      <c r="AC31">
+      <c r="AB31" s="7">
+        <f t="shared" si="3"/>
+        <v>2029</v>
+      </c>
+      <c r="AC31" s="8">
+        <f>'[3]לוח 3 table'!$D41</f>
         <v>858</v>
       </c>
-      <c r="AD31">
-        <v>1169</v>
-      </c>
-      <c r="AE31" s="1">
+      <c r="AD31" s="8">
+        <f>'[3]לוח 3 table'!$D95</f>
+        <v>1171</v>
+      </c>
+      <c r="AE31" s="7">
+        <f t="shared" si="4"/>
         <v>1654</v>
       </c>
-      <c r="AF31">
-        <v>919</v>
-      </c>
-      <c r="AG31">
-        <v>735</v>
-      </c>
-      <c r="AH31" s="1">
-        <v>1838</v>
-      </c>
-      <c r="AI31">
+      <c r="AF31" s="8">
+        <f>'[3]לוח 3 table'!$C41</f>
+        <v>920</v>
+      </c>
+      <c r="AG31" s="8">
+        <f>'[3]לוח 3 table'!$C95</f>
+        <v>734</v>
+      </c>
+      <c r="AH31" s="7">
+        <f t="shared" si="5"/>
+        <v>1837</v>
+      </c>
+      <c r="AI31" s="8">
+        <f>'[3]לוח 3 table'!$B41</f>
         <v>841</v>
       </c>
-      <c r="AJ31">
-        <v>997</v>
-      </c>
-      <c r="AK31" s="1">
+      <c r="AJ31" s="8">
+        <f>'[3]לוח 3 table'!$B95</f>
+        <v>996</v>
+      </c>
+      <c r="AK31" s="7">
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
-      <c r="AL31">
+      <c r="AL31" s="8">
+        <f>'[3]לוח 3 table'!$A41</f>
         <v>40</v>
       </c>
-      <c r="AM31">
+      <c r="AM31" s="8">
+        <f>'[3]לוח 3 table'!$A95</f>
         <v>160</v>
       </c>
     </row>
@@ -4404,102 +6667,135 @@
         <v>4.5</v>
       </c>
       <c r="G32" s="1">
-        <v>9707</v>
+        <f>'[1]לוח 1 table'!$M31</f>
+        <v>9700</v>
       </c>
       <c r="H32" s="1">
-        <v>9124</v>
+        <f>'[1]לוח 1 table'!$L31</f>
+        <v>9131</v>
       </c>
       <c r="I32" s="1">
-        <v>8581</v>
+        <f>'[1]לוח 1 table'!$K31</f>
+        <v>8608</v>
       </c>
       <c r="J32" s="1">
-        <v>4025</v>
+        <f>'[1]לוח 1 table'!$I31</f>
+        <v>4024</v>
       </c>
       <c r="K32" s="1">
+        <f>'[1]לוח 1 table'!$H31</f>
         <v>4043</v>
       </c>
       <c r="L32" s="1">
-        <v>3779</v>
+        <f>'[1]לוח 1 table'!$G31</f>
+        <v>3789</v>
       </c>
       <c r="M32" s="1">
-        <v>5682</v>
+        <f>'[1]לוח 1 table'!$D31</f>
+        <v>5676</v>
       </c>
       <c r="N32" s="1">
-        <v>5081</v>
+        <f>'[1]לוח 1 table'!$C31</f>
+        <v>5088</v>
       </c>
       <c r="O32" s="1">
-        <v>5093</v>
-      </c>
-      <c r="P32" s="1">
+        <f>'[1]לוח 1 table'!$B31</f>
+        <v>5109</v>
+      </c>
+      <c r="P32" s="7">
+        <f>'[2]2'!$E27</f>
         <v>68877</v>
       </c>
-      <c r="Q32" s="1">
-        <v>69050</v>
-      </c>
-      <c r="R32" s="1">
-        <v>68710</v>
-      </c>
-      <c r="S32" s="1">
-        <v>991</v>
-      </c>
-      <c r="T32">
-        <v>445</v>
-      </c>
-      <c r="U32">
+      <c r="Q32" s="7">
+        <f>'[2]2'!$D27</f>
+        <v>69033</v>
+      </c>
+      <c r="R32" s="7">
+        <f>'[2]2'!$C27</f>
+        <v>68722</v>
+      </c>
+      <c r="S32" s="7">
+        <f t="shared" si="0"/>
+        <v>989</v>
+      </c>
+      <c r="T32" s="8">
+        <f>'[3]לוח 3 table'!$G42</f>
+        <v>443</v>
+      </c>
+      <c r="U32" s="8">
+        <f>'[3]לוח 3 table'!$G96</f>
         <v>546</v>
       </c>
-      <c r="V32" s="1">
+      <c r="V32" s="7">
+        <f t="shared" si="1"/>
         <v>1215</v>
       </c>
-      <c r="W32">
-        <v>516</v>
-      </c>
-      <c r="X32">
-        <v>699</v>
-      </c>
-      <c r="Y32" s="1">
-        <v>1420</v>
-      </c>
-      <c r="Z32">
-        <v>446</v>
-      </c>
-      <c r="AA32">
+      <c r="W32" s="8">
+        <f>'[3]לוח 3 table'!$F42</f>
+        <v>517</v>
+      </c>
+      <c r="X32" s="8">
+        <f>'[3]לוח 3 table'!$F96</f>
+        <v>698</v>
+      </c>
+      <c r="Y32" s="7">
+        <f t="shared" si="2"/>
+        <v>1421</v>
+      </c>
+      <c r="Z32" s="8">
+        <f>'[3]לוח 3 table'!$E42</f>
+        <v>447</v>
+      </c>
+      <c r="AA32" s="8">
+        <f>'[3]לוח 3 table'!$E96</f>
         <v>974</v>
       </c>
-      <c r="AB32" s="1">
-        <v>2120</v>
-      </c>
-      <c r="AC32">
+      <c r="AB32" s="7">
+        <f t="shared" si="3"/>
+        <v>2119</v>
+      </c>
+      <c r="AC32" s="8">
+        <f>'[3]לוח 3 table'!$D42</f>
         <v>827</v>
       </c>
-      <c r="AD32">
-        <v>1293</v>
-      </c>
-      <c r="AE32" s="1">
-        <v>1598</v>
-      </c>
-      <c r="AF32">
+      <c r="AD32" s="8">
+        <f>'[3]לוח 3 table'!$D96</f>
+        <v>1292</v>
+      </c>
+      <c r="AE32" s="7">
+        <f t="shared" si="4"/>
+        <v>1595</v>
+      </c>
+      <c r="AF32" s="8">
+        <f>'[3]לוח 3 table'!$C42</f>
         <v>727</v>
       </c>
-      <c r="AG32">
-        <v>871</v>
-      </c>
-      <c r="AH32" s="1">
-        <v>2126</v>
-      </c>
-      <c r="AI32">
-        <v>1022</v>
-      </c>
-      <c r="AJ32">
-        <v>1104</v>
-      </c>
-      <c r="AK32" s="1">
+      <c r="AG32" s="8">
+        <f>'[3]לוח 3 table'!$C96</f>
+        <v>868</v>
+      </c>
+      <c r="AH32" s="7">
+        <f t="shared" si="5"/>
+        <v>2124</v>
+      </c>
+      <c r="AI32" s="8">
+        <f>'[3]לוח 3 table'!$B42</f>
+        <v>1021</v>
+      </c>
+      <c r="AJ32" s="8">
+        <f>'[3]לוח 3 table'!$B96</f>
+        <v>1103</v>
+      </c>
+      <c r="AK32" s="7">
+        <f t="shared" si="6"/>
         <v>236</v>
       </c>
-      <c r="AL32">
+      <c r="AL32" s="8">
+        <f>'[3]לוח 3 table'!$A42</f>
         <v>40</v>
       </c>
-      <c r="AM32">
+      <c r="AM32" s="8">
+        <f>'[3]לוח 3 table'!$A96</f>
         <v>196</v>
       </c>
     </row>
@@ -4523,103 +6819,136 @@
         <v>4.5</v>
       </c>
       <c r="G33" s="1">
-        <v>7981</v>
+        <f>'[1]לוח 1 table'!$M32</f>
+        <v>7983</v>
       </c>
       <c r="H33" s="1">
-        <v>8887</v>
+        <f>'[1]לוח 1 table'!$L32</f>
+        <v>8902</v>
       </c>
       <c r="I33" s="1">
-        <v>8414</v>
+        <f>'[1]לוח 1 table'!$K32</f>
+        <v>8455</v>
       </c>
       <c r="J33" s="1">
-        <v>3490</v>
+        <f>'[1]לוח 1 table'!$I32</f>
+        <v>3487</v>
       </c>
       <c r="K33" s="1">
-        <v>3728</v>
+        <f>'[1]לוח 1 table'!$H32</f>
+        <v>3726</v>
       </c>
       <c r="L33" s="1">
-        <v>3672</v>
+        <f>'[1]לוח 1 table'!$G32</f>
+        <v>3689</v>
       </c>
       <c r="M33" s="1">
-        <v>4491</v>
+        <f>'[1]לוח 1 table'!$D32</f>
+        <v>4496</v>
       </c>
       <c r="N33" s="1">
-        <v>5158</v>
+        <f>'[1]לוח 1 table'!$C32</f>
+        <v>5176</v>
       </c>
       <c r="O33" s="1">
-        <v>5202</v>
-      </c>
-      <c r="P33" s="1">
+        <f>'[1]לוח 1 table'!$B32</f>
+        <v>5232</v>
+      </c>
+      <c r="P33" s="7">
+        <f>'[2]2'!$E28</f>
         <v>68952</v>
       </c>
-      <c r="Q33" s="1">
-        <v>69503</v>
-      </c>
-      <c r="R33" s="1">
-        <v>69293</v>
-      </c>
-      <c r="S33" s="1">
-        <v>820</v>
-      </c>
-      <c r="T33">
+      <c r="Q33" s="7">
+        <f>'[2]2'!$D28</f>
+        <v>69532</v>
+      </c>
+      <c r="R33" s="7">
+        <f>'[2]2'!$C28</f>
+        <v>69302</v>
+      </c>
+      <c r="S33" s="7">
+        <f t="shared" si="0"/>
+        <v>822</v>
+      </c>
+      <c r="T33" s="8">
+        <f>'[3]לוח 3 table'!$G43</f>
         <v>409</v>
       </c>
-      <c r="U33">
-        <v>411</v>
-      </c>
-      <c r="V33" s="1">
-        <v>872</v>
-      </c>
-      <c r="W33">
-        <v>357</v>
-      </c>
-      <c r="X33">
-        <v>515</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>1179</v>
-      </c>
-      <c r="Z33">
+      <c r="U33" s="8">
+        <f>'[3]לוח 3 table'!$G97</f>
+        <v>413</v>
+      </c>
+      <c r="V33" s="7">
+        <f t="shared" si="1"/>
+        <v>873</v>
+      </c>
+      <c r="W33" s="8">
+        <f>'[3]לוח 3 table'!$F43</f>
+        <v>356</v>
+      </c>
+      <c r="X33" s="8">
+        <f>'[3]לוח 3 table'!$F97</f>
+        <v>517</v>
+      </c>
+      <c r="Y33" s="7">
+        <f t="shared" si="2"/>
+        <v>1182</v>
+      </c>
+      <c r="Z33" s="8">
+        <f>'[3]לוח 3 table'!$E43</f>
         <v>389</v>
       </c>
-      <c r="AA33">
-        <v>790</v>
-      </c>
-      <c r="AB33" s="1">
-        <v>1868</v>
-      </c>
-      <c r="AC33">
-        <v>825</v>
-      </c>
-      <c r="AD33">
-        <v>1043</v>
-      </c>
-      <c r="AE33" s="1">
-        <v>1379</v>
-      </c>
-      <c r="AF33">
-        <v>708</v>
-      </c>
-      <c r="AG33">
+      <c r="AA33" s="8">
+        <f>'[3]לוח 3 table'!$E97</f>
+        <v>793</v>
+      </c>
+      <c r="AB33" s="7">
+        <f t="shared" si="3"/>
+        <v>1865</v>
+      </c>
+      <c r="AC33" s="8">
+        <f>'[3]לוח 3 table'!$D43</f>
+        <v>821</v>
+      </c>
+      <c r="AD33" s="8">
+        <f>'[3]לוח 3 table'!$D97</f>
+        <v>1044</v>
+      </c>
+      <c r="AE33" s="7">
+        <f t="shared" si="4"/>
+        <v>1381</v>
+      </c>
+      <c r="AF33" s="8">
+        <f>'[3]לוח 3 table'!$C43</f>
+        <v>710</v>
+      </c>
+      <c r="AG33" s="8">
+        <f>'[3]לוח 3 table'!$C97</f>
         <v>671</v>
       </c>
-      <c r="AH33" s="1">
-        <v>1660</v>
-      </c>
-      <c r="AI33">
+      <c r="AH33" s="7">
+        <f t="shared" si="5"/>
+        <v>1658</v>
+      </c>
+      <c r="AI33" s="8">
+        <f>'[3]לוח 3 table'!$B43</f>
         <v>758</v>
       </c>
-      <c r="AJ33">
-        <v>902</v>
-      </c>
-      <c r="AK33" s="1">
-        <v>204</v>
-      </c>
-      <c r="AL33">
+      <c r="AJ33" s="8">
+        <f>'[3]לוח 3 table'!$B97</f>
+        <v>900</v>
+      </c>
+      <c r="AK33" s="7">
+        <f t="shared" si="6"/>
+        <v>202</v>
+      </c>
+      <c r="AL33" s="8">
+        <f>'[3]לוח 3 table'!$A43</f>
         <v>44</v>
       </c>
-      <c r="AM33">
-        <v>160</v>
+      <c r="AM33" s="8">
+        <f>'[3]לוח 3 table'!$A97</f>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.3">
@@ -4642,102 +6971,135 @@
         <v>4.5</v>
       </c>
       <c r="G34" s="1">
-        <v>9064</v>
+        <f>'[1]לוח 1 table'!$M33</f>
+        <v>9000</v>
       </c>
       <c r="H34" s="1">
-        <v>8590</v>
+        <f>'[1]לוח 1 table'!$L33</f>
+        <v>8597</v>
       </c>
       <c r="I34" s="1">
-        <v>8217</v>
+        <f>'[1]לוח 1 table'!$K33</f>
+        <v>8283</v>
       </c>
       <c r="J34" s="1">
-        <v>3821</v>
+        <f>'[1]לוח 1 table'!$I33</f>
+        <v>3736</v>
       </c>
       <c r="K34" s="1">
-        <v>3484</v>
+        <f>'[1]לוח 1 table'!$H33</f>
+        <v>3467</v>
       </c>
       <c r="L34" s="1">
-        <v>3553</v>
+        <f>'[1]לוח 1 table'!$G33</f>
+        <v>3579</v>
       </c>
       <c r="M34" s="1">
-        <v>5243</v>
+        <f>'[1]לוח 1 table'!$D33</f>
+        <v>5264</v>
       </c>
       <c r="N34" s="1">
-        <v>5105</v>
+        <f>'[1]לוח 1 table'!$C33</f>
+        <v>5130</v>
       </c>
       <c r="O34" s="1">
-        <v>5278</v>
-      </c>
-      <c r="P34" s="1">
+        <f>'[1]לוח 1 table'!$B33</f>
+        <v>5332</v>
+      </c>
+      <c r="P34" s="7">
+        <f>'[2]2'!$E29</f>
         <v>69744</v>
       </c>
-      <c r="Q34" s="1">
-        <v>69130</v>
-      </c>
-      <c r="R34" s="1">
-        <v>70094</v>
-      </c>
-      <c r="S34" s="1">
-        <v>1000</v>
-      </c>
-      <c r="T34">
-        <v>518</v>
-      </c>
-      <c r="U34">
-        <v>482</v>
-      </c>
-      <c r="V34" s="1">
-        <v>770</v>
-      </c>
-      <c r="W34">
-        <v>229</v>
-      </c>
-      <c r="X34">
+      <c r="Q34" s="7">
+        <f>'[2]2'!$D29</f>
+        <v>69233</v>
+      </c>
+      <c r="R34" s="7">
+        <f>'[2]2'!$C29</f>
+        <v>70091</v>
+      </c>
+      <c r="S34" s="7">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="T34" s="8">
+        <f>'[3]לוח 3 table'!$G44</f>
+        <v>444</v>
+      </c>
+      <c r="U34" s="8">
+        <f>'[3]לוח 3 table'!$G98</f>
+        <v>486</v>
+      </c>
+      <c r="V34" s="7">
+        <f t="shared" si="1"/>
+        <v>767</v>
+      </c>
+      <c r="W34" s="8">
+        <f>'[3]לוח 3 table'!$F44</f>
+        <v>226</v>
+      </c>
+      <c r="X34" s="8">
+        <f>'[3]לוח 3 table'!$F98</f>
         <v>541</v>
       </c>
-      <c r="Y34" s="1">
-        <v>1531</v>
-      </c>
-      <c r="Z34">
+      <c r="Y34" s="7">
+        <f t="shared" si="2"/>
+        <v>1542</v>
+      </c>
+      <c r="Z34" s="8">
+        <f>'[3]לוח 3 table'!$E44</f>
         <v>483</v>
       </c>
-      <c r="AA34">
-        <v>1048</v>
-      </c>
-      <c r="AB34" s="1">
-        <v>2050</v>
-      </c>
-      <c r="AC34">
-        <v>872</v>
-      </c>
-      <c r="AD34">
-        <v>1178</v>
-      </c>
-      <c r="AE34" s="1">
-        <v>1459</v>
-      </c>
-      <c r="AF34">
-        <v>709</v>
-      </c>
-      <c r="AG34">
-        <v>750</v>
-      </c>
-      <c r="AH34" s="1">
-        <v>1994</v>
-      </c>
-      <c r="AI34">
-        <v>942</v>
-      </c>
-      <c r="AJ34">
-        <v>1052</v>
-      </c>
-      <c r="AK34" s="1">
+      <c r="AA34" s="8">
+        <f>'[3]לוח 3 table'!$E98</f>
+        <v>1059</v>
+      </c>
+      <c r="AB34" s="7">
+        <f t="shared" si="3"/>
+        <v>2033</v>
+      </c>
+      <c r="AC34" s="8">
+        <f>'[3]לוח 3 table'!$D44</f>
+        <v>852</v>
+      </c>
+      <c r="AD34" s="8">
+        <f>'[3]לוח 3 table'!$D98</f>
+        <v>1181</v>
+      </c>
+      <c r="AE34" s="7">
+        <f t="shared" si="4"/>
+        <v>1471</v>
+      </c>
+      <c r="AF34" s="8">
+        <f>'[3]לוח 3 table'!$C44</f>
+        <v>718</v>
+      </c>
+      <c r="AG34" s="8">
+        <f>'[3]לוח 3 table'!$C98</f>
+        <v>753</v>
+      </c>
+      <c r="AH34" s="7">
+        <f t="shared" si="5"/>
+        <v>1995</v>
+      </c>
+      <c r="AI34" s="8">
+        <f>'[3]לוח 3 table'!$B44</f>
+        <v>944</v>
+      </c>
+      <c r="AJ34" s="8">
+        <f>'[3]לוח 3 table'!$B98</f>
+        <v>1051</v>
+      </c>
+      <c r="AK34" s="7">
+        <f t="shared" si="6"/>
         <v>262</v>
       </c>
-      <c r="AL34">
+      <c r="AL34" s="8">
+        <f>'[3]לוח 3 table'!$A44</f>
         <v>69</v>
       </c>
-      <c r="AM34">
+      <c r="AM34" s="8">
+        <f>'[3]לוח 3 table'!$A98</f>
         <v>193</v>
       </c>
     </row>
@@ -4761,103 +7123,136 @@
         <v>4.5</v>
       </c>
       <c r="G35" s="1">
-        <v>5496</v>
+        <f>'[1]לוח 1 table'!$M34</f>
+        <v>5594</v>
       </c>
       <c r="H35" s="1">
-        <v>7265</v>
+        <f>'[1]לוח 1 table'!$L34</f>
+        <v>7408</v>
       </c>
       <c r="I35" s="1">
-        <v>8036</v>
+        <f>'[1]לוח 1 table'!$K34</f>
+        <v>8129</v>
       </c>
       <c r="J35" s="1">
-        <v>2394</v>
+        <f>'[1]לוח 1 table'!$I34</f>
+        <v>2400</v>
       </c>
       <c r="K35" s="1">
-        <v>3402</v>
+        <f>'[1]לוח 1 table'!$H34</f>
+        <v>3455</v>
       </c>
       <c r="L35" s="1">
-        <v>3437</v>
+        <f>'[1]לוח 1 table'!$G34</f>
+        <v>3467</v>
       </c>
       <c r="M35" s="1">
-        <v>3102</v>
+        <f>'[1]לוח 1 table'!$D34</f>
+        <v>3194</v>
       </c>
       <c r="N35" s="1">
-        <v>3863</v>
+        <f>'[1]לוח 1 table'!$C34</f>
+        <v>3952</v>
       </c>
       <c r="O35" s="1">
-        <v>5305</v>
-      </c>
-      <c r="P35" s="1">
-        <v>69775</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>70160</v>
-      </c>
-      <c r="R35" s="1">
-        <v>71152</v>
-      </c>
-      <c r="S35" s="1">
-        <v>468</v>
-      </c>
-      <c r="T35">
+        <f>'[1]לוח 1 table'!$B34</f>
+        <v>5385</v>
+      </c>
+      <c r="P35" s="7">
+        <f>'[2]2'!$E30</f>
+        <v>69943</v>
+      </c>
+      <c r="Q35" s="7">
+        <f>'[2]2'!$D30</f>
+        <v>70349</v>
+      </c>
+      <c r="R35" s="7">
+        <f>'[2]2'!$C30</f>
+        <v>71145</v>
+      </c>
+      <c r="S35" s="7">
+        <f t="shared" si="0"/>
+        <v>471</v>
+      </c>
+      <c r="T35" s="8">
+        <f>'[3]לוח 3 table'!$G45</f>
         <v>194</v>
       </c>
-      <c r="U35">
-        <v>274</v>
-      </c>
-      <c r="V35" s="1">
-        <v>591</v>
-      </c>
-      <c r="W35">
+      <c r="U35" s="8">
+        <f>'[3]לוח 3 table'!$G99</f>
+        <v>277</v>
+      </c>
+      <c r="V35" s="7">
+        <f t="shared" si="1"/>
+        <v>597</v>
+      </c>
+      <c r="W35" s="8">
+        <f>'[3]לוח 3 table'!$F45</f>
         <v>239</v>
       </c>
-      <c r="X35">
-        <v>352</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>834</v>
-      </c>
-      <c r="Z35">
+      <c r="X35" s="8">
+        <f>'[3]לוח 3 table'!$F99</f>
+        <v>358</v>
+      </c>
+      <c r="Y35" s="7">
+        <f t="shared" si="2"/>
+        <v>853</v>
+      </c>
+      <c r="Z35" s="8">
+        <f>'[3]לוח 3 table'!$E45</f>
         <v>267</v>
       </c>
-      <c r="AA35">
-        <v>567</v>
-      </c>
-      <c r="AB35" s="1">
-        <v>1304</v>
-      </c>
-      <c r="AC35">
-        <v>605</v>
-      </c>
-      <c r="AD35">
-        <v>699</v>
-      </c>
-      <c r="AE35" s="1">
-        <v>875</v>
-      </c>
-      <c r="AF35">
-        <v>415</v>
-      </c>
-      <c r="AG35">
-        <v>460</v>
-      </c>
-      <c r="AH35" s="1">
-        <v>1299</v>
-      </c>
-      <c r="AI35">
+      <c r="AA35" s="8">
+        <f>'[3]לוח 3 table'!$E99</f>
+        <v>586</v>
+      </c>
+      <c r="AB35" s="7">
+        <f t="shared" si="3"/>
+        <v>1341</v>
+      </c>
+      <c r="AC35" s="8">
+        <f>'[3]לוח 3 table'!$D45</f>
+        <v>610</v>
+      </c>
+      <c r="AD35" s="8">
+        <f>'[3]לוח 3 table'!$D99</f>
+        <v>731</v>
+      </c>
+      <c r="AE35" s="7">
+        <f t="shared" si="4"/>
+        <v>901</v>
+      </c>
+      <c r="AF35" s="8">
+        <f>'[3]לוח 3 table'!$C45</f>
+        <v>416</v>
+      </c>
+      <c r="AG35" s="8">
+        <f>'[3]לוח 3 table'!$C99</f>
+        <v>485</v>
+      </c>
+      <c r="AH35" s="7">
+        <f t="shared" si="5"/>
+        <v>1302</v>
+      </c>
+      <c r="AI35" s="8">
+        <f>'[3]לוח 3 table'!$B45</f>
         <v>633</v>
       </c>
-      <c r="AJ35">
-        <v>666</v>
-      </c>
-      <c r="AK35" s="1">
-        <v>124</v>
-      </c>
-      <c r="AL35">
+      <c r="AJ35" s="8">
+        <f>'[3]לוח 3 table'!$B99</f>
+        <v>669</v>
+      </c>
+      <c r="AK35" s="7">
+        <f t="shared" si="6"/>
+        <v>125</v>
+      </c>
+      <c r="AL35" s="8">
+        <f>'[3]לוח 3 table'!$A45</f>
         <v>39</v>
       </c>
-      <c r="AM35">
-        <v>85</v>
+      <c r="AM35" s="8">
+        <f>'[3]לוח 3 table'!$A99</f>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.3">
@@ -4880,103 +7275,136 @@
         <v>4.5</v>
       </c>
       <c r="G36" s="1">
-        <v>7453</v>
+        <f>'[1]לוח 1 table'!$M35</f>
+        <v>7544</v>
       </c>
       <c r="H36" s="1">
-        <v>7221</v>
+        <f>'[1]לוח 1 table'!$L35</f>
+        <v>7272</v>
       </c>
       <c r="I36" s="1">
-        <v>7894</v>
+        <f>'[1]לוח 1 table'!$K35</f>
+        <v>8012</v>
       </c>
       <c r="J36" s="1">
-        <v>3133</v>
+        <f>'[1]לוח 1 table'!$I35</f>
+        <v>3130</v>
       </c>
       <c r="K36" s="1">
-        <v>3069</v>
+        <f>'[1]לוח 1 table'!$H35</f>
+        <v>3041</v>
       </c>
       <c r="L36" s="1">
-        <v>3329</v>
+        <f>'[1]לוח 1 table'!$G35</f>
+        <v>3356</v>
       </c>
       <c r="M36" s="1">
-        <v>4320</v>
+        <f>'[1]לוח 1 table'!$D35</f>
+        <v>4414</v>
       </c>
       <c r="N36" s="1">
-        <v>4152</v>
+        <f>'[1]לוח 1 table'!$C35</f>
+        <v>4231</v>
       </c>
       <c r="O36" s="1">
-        <v>5269</v>
-      </c>
-      <c r="P36" s="1">
-        <v>71508</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>71975</v>
-      </c>
-      <c r="R36" s="1">
-        <v>72459</v>
-      </c>
-      <c r="S36" s="1">
-        <v>663</v>
-      </c>
-      <c r="T36">
-        <v>257</v>
-      </c>
-      <c r="U36">
-        <v>406</v>
-      </c>
-      <c r="V36" s="1">
-        <v>797</v>
-      </c>
-      <c r="W36">
+        <f>'[1]לוח 1 table'!$B35</f>
+        <v>5375</v>
+      </c>
+      <c r="P36" s="7">
+        <f>'[2]2'!$E31</f>
+        <v>71690</v>
+      </c>
+      <c r="Q36" s="7">
+        <f>'[2]2'!$D31</f>
+        <v>72151</v>
+      </c>
+      <c r="R36" s="7">
+        <f>'[2]2'!$C31</f>
+        <v>72470</v>
+      </c>
+      <c r="S36" s="7">
+        <f t="shared" si="0"/>
+        <v>673</v>
+      </c>
+      <c r="T36" s="8">
+        <f>'[3]לוח 3 table'!$G46</f>
+        <v>258</v>
+      </c>
+      <c r="U36" s="8">
+        <f>'[3]לוח 3 table'!$G100</f>
+        <v>415</v>
+      </c>
+      <c r="V36" s="7">
+        <f t="shared" si="1"/>
+        <v>810</v>
+      </c>
+      <c r="W36" s="8">
+        <f>'[3]לוח 3 table'!$F46</f>
         <v>333</v>
       </c>
-      <c r="X36">
-        <v>464</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>1081</v>
-      </c>
-      <c r="Z36">
-        <v>355</v>
-      </c>
-      <c r="AA36">
-        <v>726</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>1802</v>
-      </c>
-      <c r="AC36">
-        <v>795</v>
-      </c>
-      <c r="AD36">
-        <v>1007</v>
-      </c>
-      <c r="AE36" s="1">
-        <v>1205</v>
-      </c>
-      <c r="AF36">
-        <v>541</v>
-      </c>
-      <c r="AG36">
-        <v>664</v>
-      </c>
-      <c r="AH36" s="1">
-        <v>1726</v>
-      </c>
-      <c r="AI36">
-        <v>792</v>
-      </c>
-      <c r="AJ36">
+      <c r="X36" s="8">
+        <f>'[3]לוח 3 table'!$F100</f>
+        <v>477</v>
+      </c>
+      <c r="Y36" s="7">
+        <f t="shared" si="2"/>
+        <v>1101</v>
+      </c>
+      <c r="Z36" s="8">
+        <f>'[3]לוח 3 table'!$E46</f>
+        <v>356</v>
+      </c>
+      <c r="AA36" s="8">
+        <f>'[3]לוח 3 table'!$E100</f>
+        <v>745</v>
+      </c>
+      <c r="AB36" s="7">
+        <f t="shared" si="3"/>
+        <v>1804</v>
+      </c>
+      <c r="AC36" s="8">
+        <f>'[3]לוח 3 table'!$D46</f>
+        <v>769</v>
+      </c>
+      <c r="AD36" s="8">
+        <f>'[3]לוח 3 table'!$D100</f>
+        <v>1035</v>
+      </c>
+      <c r="AE36" s="7">
+        <f t="shared" si="4"/>
+        <v>1251</v>
+      </c>
+      <c r="AF36" s="8">
+        <f>'[3]לוח 3 table'!$C46</f>
+        <v>562</v>
+      </c>
+      <c r="AG36" s="8">
+        <f>'[3]לוח 3 table'!$C100</f>
+        <v>689</v>
+      </c>
+      <c r="AH36" s="7">
+        <f t="shared" si="5"/>
+        <v>1725</v>
+      </c>
+      <c r="AI36" s="8">
+        <f>'[3]לוח 3 table'!$B46</f>
+        <v>791</v>
+      </c>
+      <c r="AJ36" s="8">
+        <f>'[3]לוח 3 table'!$B100</f>
         <v>934</v>
       </c>
-      <c r="AK36" s="1">
-        <v>180</v>
-      </c>
-      <c r="AL36">
+      <c r="AK36" s="7">
+        <f t="shared" si="6"/>
+        <v>181</v>
+      </c>
+      <c r="AL36" s="8">
+        <f>'[3]לוח 3 table'!$A46</f>
         <v>61</v>
       </c>
-      <c r="AM36">
-        <v>119</v>
+      <c r="AM36" s="8">
+        <f>'[3]לוח 3 table'!$A100</f>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.3">
@@ -4999,102 +7427,135 @@
         <v>4.5</v>
       </c>
       <c r="G37" s="1">
-        <v>12052</v>
+        <f>'[1]לוח 1 table'!$M36</f>
+        <v>12300</v>
       </c>
       <c r="H37" s="1">
-        <v>10209</v>
+        <f>'[1]לוח 1 table'!$L36</f>
+        <v>10432</v>
       </c>
       <c r="I37" s="1">
-        <v>7797</v>
+        <f>'[1]לוח 1 table'!$K36</f>
+        <v>7928</v>
       </c>
       <c r="J37" s="1">
-        <v>6423</v>
+        <f>'[1]לוח 1 table'!$I36</f>
+        <v>6518</v>
       </c>
       <c r="K37" s="1">
-        <v>4912</v>
+        <f>'[1]לוח 1 table'!$H36</f>
+        <v>4995</v>
       </c>
       <c r="L37" s="1">
-        <v>3232</v>
+        <f>'[1]לוח 1 table'!$G36</f>
+        <v>3248</v>
       </c>
       <c r="M37" s="1">
-        <v>5629</v>
+        <f>'[1]לוח 1 table'!$D36</f>
+        <v>5782</v>
       </c>
       <c r="N37" s="1">
+        <f>'[1]לוח 1 table'!$C36</f>
+        <v>5438</v>
+      </c>
+      <c r="O37" s="1">
+        <f>'[1]לוח 1 table'!$B36</f>
         <v>5297</v>
       </c>
-      <c r="O37" s="1">
-        <v>5173</v>
-      </c>
-      <c r="P37" s="1">
-        <v>76174</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>73540</v>
-      </c>
-      <c r="R37" s="1">
-        <v>73938</v>
-      </c>
-      <c r="S37" s="1">
-        <v>1053</v>
-      </c>
-      <c r="T37">
-        <v>547</v>
-      </c>
-      <c r="U37">
-        <v>506</v>
-      </c>
-      <c r="V37" s="1">
-        <v>1304</v>
-      </c>
-      <c r="W37">
-        <v>640</v>
-      </c>
-      <c r="X37">
-        <v>664</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>1667</v>
-      </c>
-      <c r="Z37">
-        <v>720</v>
-      </c>
-      <c r="AA37">
-        <v>947</v>
-      </c>
-      <c r="AB37" s="1">
-        <v>2764</v>
-      </c>
-      <c r="AC37">
-        <v>1467</v>
-      </c>
-      <c r="AD37">
-        <v>1297</v>
-      </c>
-      <c r="AE37" s="1">
-        <v>2131</v>
-      </c>
-      <c r="AF37">
-        <v>1261</v>
-      </c>
-      <c r="AG37">
-        <v>870</v>
-      </c>
-      <c r="AH37" s="1">
-        <v>2846</v>
-      </c>
-      <c r="AI37">
-        <v>1686</v>
-      </c>
-      <c r="AJ37">
-        <v>1160</v>
-      </c>
-      <c r="AK37" s="1">
-        <v>288</v>
-      </c>
-      <c r="AL37">
-        <v>102</v>
-      </c>
-      <c r="AM37">
+      <c r="P37" s="7">
+        <f>'[2]2'!$E32</f>
+        <v>76349</v>
+      </c>
+      <c r="Q37" s="7">
+        <f>'[2]2'!$D32</f>
+        <v>73614</v>
+      </c>
+      <c r="R37" s="7">
+        <f>'[2]2'!$C32</f>
+        <v>74015</v>
+      </c>
+      <c r="S37" s="7">
+        <f t="shared" si="0"/>
+        <v>1073</v>
+      </c>
+      <c r="T37" s="8">
+        <f>'[3]לוח 3 table'!$G47</f>
+        <v>545</v>
+      </c>
+      <c r="U37" s="8">
+        <f>'[3]לוח 3 table'!$G101</f>
+        <v>528</v>
+      </c>
+      <c r="V37" s="7">
+        <f t="shared" si="1"/>
+        <v>1313</v>
+      </c>
+      <c r="W37" s="8">
+        <f>'[3]לוח 3 table'!$F47</f>
+        <v>639</v>
+      </c>
+      <c r="X37" s="8">
+        <f>'[3]לוח 3 table'!$F101</f>
+        <v>674</v>
+      </c>
+      <c r="Y37" s="7">
+        <f t="shared" si="2"/>
+        <v>1691</v>
+      </c>
+      <c r="Z37" s="8">
+        <f>'[3]לוח 3 table'!$E47</f>
+        <v>721</v>
+      </c>
+      <c r="AA37" s="8">
+        <f>'[3]לוח 3 table'!$E101</f>
+        <v>970</v>
+      </c>
+      <c r="AB37" s="7">
+        <f t="shared" si="3"/>
+        <v>2827</v>
+      </c>
+      <c r="AC37" s="8">
+        <f>'[3]לוח 3 table'!$D47</f>
+        <v>1484</v>
+      </c>
+      <c r="AD37" s="8">
+        <f>'[3]לוח 3 table'!$D101</f>
+        <v>1343</v>
+      </c>
+      <c r="AE37" s="7">
+        <f t="shared" si="4"/>
+        <v>2247</v>
+      </c>
+      <c r="AF37" s="8">
+        <f>'[3]לוח 3 table'!$C47</f>
+        <v>1331</v>
+      </c>
+      <c r="AG37" s="8">
+        <f>'[3]לוח 3 table'!$C101</f>
+        <v>916</v>
+      </c>
+      <c r="AH37" s="7">
+        <f t="shared" si="5"/>
+        <v>2856</v>
+      </c>
+      <c r="AI37" s="8">
+        <f>'[3]לוח 3 table'!$B47</f>
+        <v>1692</v>
+      </c>
+      <c r="AJ37" s="8">
+        <f>'[3]לוח 3 table'!$B101</f>
+        <v>1164</v>
+      </c>
+      <c r="AK37" s="7">
+        <f t="shared" si="6"/>
+        <v>292</v>
+      </c>
+      <c r="AL37" s="8">
+        <f>'[3]לוח 3 table'!$A47</f>
+        <v>106</v>
+      </c>
+      <c r="AM37" s="8">
+        <f>'[3]לוח 3 table'!$A101</f>
         <v>186</v>
       </c>
     </row>
@@ -5118,103 +7579,136 @@
         <v>4.5</v>
       </c>
       <c r="G38" s="1">
-        <v>8074</v>
+        <f>'[1]לוח 1 table'!$M37</f>
+        <v>8266</v>
       </c>
       <c r="H38" s="1">
-        <v>8298</v>
+        <f>'[1]לוח 1 table'!$L37</f>
+        <v>8492</v>
       </c>
       <c r="I38" s="1">
-        <v>7729</v>
+        <f>'[1]לוח 1 table'!$K37</f>
+        <v>7856</v>
       </c>
       <c r="J38" s="1">
-        <v>3159</v>
+        <f>'[1]לוח 1 table'!$I37</f>
+        <v>3192</v>
       </c>
       <c r="K38" s="1">
-        <v>3265</v>
+        <f>'[1]לוח 1 table'!$H37</f>
+        <v>3307</v>
       </c>
       <c r="L38" s="1">
-        <v>3144</v>
+        <f>'[1]לוח 1 table'!$G37</f>
+        <v>3145</v>
       </c>
       <c r="M38" s="1">
-        <v>4915</v>
+        <f>'[1]לוח 1 table'!$D37</f>
+        <v>5074</v>
       </c>
       <c r="N38" s="1">
-        <v>5032</v>
+        <f>'[1]לוח 1 table'!$C37</f>
+        <v>5186</v>
       </c>
       <c r="O38" s="1">
-        <v>5030</v>
-      </c>
-      <c r="P38" s="1">
-        <v>77633</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>75436</v>
-      </c>
-      <c r="R38" s="1">
-        <v>75443</v>
-      </c>
-      <c r="S38" s="1">
-        <v>719</v>
-      </c>
-      <c r="T38">
-        <v>249</v>
-      </c>
-      <c r="U38">
-        <v>470</v>
-      </c>
-      <c r="V38" s="1">
-        <v>1014</v>
-      </c>
-      <c r="W38">
+        <f>'[1]לוח 1 table'!$B37</f>
+        <v>5164</v>
+      </c>
+      <c r="P38" s="7">
+        <f>'[2]2'!$E33</f>
+        <v>77569</v>
+      </c>
+      <c r="Q38" s="7">
+        <f>'[2]2'!$D33</f>
+        <v>75419</v>
+      </c>
+      <c r="R38" s="7">
+        <f>'[2]2'!$C33</f>
+        <v>75662</v>
+      </c>
+      <c r="S38" s="7">
+        <f t="shared" si="0"/>
+        <v>727</v>
+      </c>
+      <c r="T38" s="8">
+        <f>'[3]לוח 3 table'!$G48</f>
+        <v>251</v>
+      </c>
+      <c r="U38" s="8">
+        <f>'[3]לוח 3 table'!$G102</f>
+        <v>476</v>
+      </c>
+      <c r="V38" s="7">
+        <f t="shared" si="1"/>
+        <v>1031</v>
+      </c>
+      <c r="W38" s="8">
+        <f>'[3]לוח 3 table'!$F48</f>
         <v>321</v>
       </c>
-      <c r="X38">
-        <v>693</v>
-      </c>
-      <c r="Y38" s="1">
-        <v>1100</v>
-      </c>
-      <c r="Z38">
-        <v>306</v>
-      </c>
-      <c r="AA38">
-        <v>794</v>
-      </c>
-      <c r="AB38" s="1">
-        <v>2072</v>
-      </c>
-      <c r="AC38">
-        <v>960</v>
-      </c>
-      <c r="AD38">
-        <v>1112</v>
-      </c>
-      <c r="AE38" s="1">
-        <v>1261</v>
-      </c>
-      <c r="AF38">
-        <v>569</v>
-      </c>
-      <c r="AG38">
-        <v>692</v>
-      </c>
-      <c r="AH38" s="1">
-        <v>1715</v>
-      </c>
-      <c r="AI38">
-        <v>707</v>
-      </c>
-      <c r="AJ38">
-        <v>1008</v>
-      </c>
-      <c r="AK38" s="1">
-        <v>192</v>
-      </c>
-      <c r="AL38">
-        <v>45</v>
-      </c>
-      <c r="AM38">
-        <v>147</v>
+      <c r="X38" s="8">
+        <f>'[3]לוח 3 table'!$F102</f>
+        <v>710</v>
+      </c>
+      <c r="Y38" s="7">
+        <f t="shared" si="2"/>
+        <v>1135</v>
+      </c>
+      <c r="Z38" s="8">
+        <f>'[3]לוח 3 table'!$E48</f>
+        <v>316</v>
+      </c>
+      <c r="AA38" s="8">
+        <f>'[3]לוח 3 table'!$E102</f>
+        <v>819</v>
+      </c>
+      <c r="AB38" s="7">
+        <f t="shared" si="3"/>
+        <v>2135</v>
+      </c>
+      <c r="AC38" s="8">
+        <f>'[3]לוח 3 table'!$D48</f>
+        <v>979</v>
+      </c>
+      <c r="AD38" s="8">
+        <f>'[3]לוח 3 table'!$D102</f>
+        <v>1156</v>
+      </c>
+      <c r="AE38" s="7">
+        <f t="shared" si="4"/>
+        <v>1299</v>
+      </c>
+      <c r="AF38" s="8">
+        <f>'[3]לוח 3 table'!$C48</f>
+        <v>568</v>
+      </c>
+      <c r="AG38" s="8">
+        <f>'[3]לוח 3 table'!$C102</f>
+        <v>731</v>
+      </c>
+      <c r="AH38" s="7">
+        <f t="shared" si="5"/>
+        <v>1741</v>
+      </c>
+      <c r="AI38" s="8">
+        <f>'[3]לוח 3 table'!$B48</f>
+        <v>711</v>
+      </c>
+      <c r="AJ38" s="8">
+        <f>'[3]לוח 3 table'!$B102</f>
+        <v>1030</v>
+      </c>
+      <c r="AK38" s="7">
+        <f t="shared" si="6"/>
+        <v>197</v>
+      </c>
+      <c r="AL38" s="8">
+        <f>'[3]לוח 3 table'!$A48</f>
+        <v>46</v>
+      </c>
+      <c r="AM38" s="8">
+        <f>'[3]לוח 3 table'!$A102</f>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.3">
@@ -5237,103 +7731,136 @@
         <v>4.5</v>
       </c>
       <c r="G39" s="1">
-        <v>7649</v>
+        <f>'[1]לוח 1 table'!$M38</f>
+        <v>7819</v>
       </c>
       <c r="H39" s="1">
-        <v>7839</v>
+        <f>'[1]לוח 1 table'!$L38</f>
+        <v>7997</v>
       </c>
       <c r="I39" s="1">
-        <v>7665</v>
+        <f>'[1]לוח 1 table'!$K38</f>
+        <v>7769</v>
       </c>
       <c r="J39" s="1">
-        <v>2983</v>
+        <f>'[1]לוח 1 table'!$I38</f>
+        <v>3025</v>
       </c>
       <c r="K39" s="1">
-        <v>3096</v>
+        <f>'[1]לוח 1 table'!$H38</f>
+        <v>3124</v>
       </c>
       <c r="L39" s="1">
-        <v>3063</v>
+        <f>'[1]לוח 1 table'!$G38</f>
+        <v>3044</v>
       </c>
       <c r="M39" s="1">
-        <v>4666</v>
+        <f>'[1]לוח 1 table'!$D38</f>
+        <v>4794</v>
       </c>
       <c r="N39" s="1">
-        <v>4742</v>
+        <f>'[1]לוח 1 table'!$C38</f>
+        <v>4873</v>
       </c>
       <c r="O39" s="1">
-        <v>4867</v>
-      </c>
-      <c r="P39" s="1">
-        <v>77752</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>78410</v>
-      </c>
-      <c r="R39" s="1">
-        <v>76795</v>
-      </c>
-      <c r="S39" s="1">
-        <v>763</v>
-      </c>
-      <c r="T39">
-        <v>321</v>
-      </c>
-      <c r="U39">
-        <v>442</v>
-      </c>
-      <c r="V39" s="1">
-        <v>830</v>
-      </c>
-      <c r="W39">
-        <v>246</v>
-      </c>
-      <c r="X39">
-        <v>584</v>
-      </c>
-      <c r="Y39" s="1">
-        <v>1101</v>
-      </c>
-      <c r="Z39">
-        <v>326</v>
-      </c>
-      <c r="AA39">
-        <v>775</v>
-      </c>
-      <c r="AB39" s="1">
-        <v>1920</v>
-      </c>
-      <c r="AC39">
-        <v>842</v>
-      </c>
-      <c r="AD39">
-        <v>1078</v>
-      </c>
-      <c r="AE39" s="1">
-        <v>1259</v>
-      </c>
-      <c r="AF39">
-        <v>577</v>
-      </c>
-      <c r="AG39">
-        <v>682</v>
-      </c>
-      <c r="AH39" s="1">
-        <v>1556</v>
-      </c>
-      <c r="AI39">
-        <v>621</v>
-      </c>
-      <c r="AJ39">
-        <v>935</v>
-      </c>
-      <c r="AK39" s="1">
-        <v>204</v>
-      </c>
-      <c r="AL39">
+        <f>'[1]לוח 1 table'!$B38</f>
+        <v>4997</v>
+      </c>
+      <c r="P39" s="7">
+        <f>'[2]2'!$E34</f>
+        <v>77506</v>
+      </c>
+      <c r="Q39" s="7">
+        <f>'[2]2'!$D34</f>
+        <v>78293</v>
+      </c>
+      <c r="R39" s="7">
+        <f>'[2]2'!$C34</f>
+        <v>77241</v>
+      </c>
+      <c r="S39" s="7">
+        <f t="shared" si="0"/>
+        <v>782</v>
+      </c>
+      <c r="T39" s="8">
+        <f>'[3]לוח 3 table'!$G49</f>
+        <v>328</v>
+      </c>
+      <c r="U39" s="8">
+        <f>'[3]לוח 3 table'!$G103</f>
+        <v>454</v>
+      </c>
+      <c r="V39" s="7">
+        <f t="shared" si="1"/>
+        <v>835</v>
+      </c>
+      <c r="W39" s="8">
+        <f>'[3]לוח 3 table'!$F49</f>
+        <v>243</v>
+      </c>
+      <c r="X39" s="8">
+        <f>'[3]לוח 3 table'!$F103</f>
+        <v>592</v>
+      </c>
+      <c r="Y39" s="7">
+        <f t="shared" si="2"/>
+        <v>1133</v>
+      </c>
+      <c r="Z39" s="8">
+        <f>'[3]לוח 3 table'!$E49</f>
+        <v>340</v>
+      </c>
+      <c r="AA39" s="8">
+        <f>'[3]לוח 3 table'!$E103</f>
+        <v>793</v>
+      </c>
+      <c r="AB39" s="7">
+        <f t="shared" si="3"/>
+        <v>1987</v>
+      </c>
+      <c r="AC39" s="8">
+        <f>'[3]לוח 3 table'!$D49</f>
+        <v>873</v>
+      </c>
+      <c r="AD39" s="8">
+        <f>'[3]לוח 3 table'!$D103</f>
+        <v>1114</v>
+      </c>
+      <c r="AE39" s="7">
+        <f t="shared" si="4"/>
+        <v>1296</v>
+      </c>
+      <c r="AF39" s="8">
+        <f>'[3]לוח 3 table'!$C49</f>
+        <v>579</v>
+      </c>
+      <c r="AG39" s="8">
+        <f>'[3]לוח 3 table'!$C103</f>
+        <v>717</v>
+      </c>
+      <c r="AH39" s="7">
+        <f t="shared" si="5"/>
+        <v>1575</v>
+      </c>
+      <c r="AI39" s="8">
+        <f>'[3]לוח 3 table'!$B49</f>
+        <v>625</v>
+      </c>
+      <c r="AJ39" s="8">
+        <f>'[3]לוח 3 table'!$B103</f>
+        <v>950</v>
+      </c>
+      <c r="AK39" s="7">
+        <f t="shared" si="6"/>
+        <v>207</v>
+      </c>
+      <c r="AL39" s="8">
+        <f>'[3]לוח 3 table'!$A49</f>
         <v>35</v>
       </c>
-      <c r="AM39">
-        <v>169</v>
+      <c r="AM39" s="8">
+        <f>'[3]לוח 3 table'!$A103</f>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.3">
@@ -5356,111 +7883,289 @@
         <v>4.5</v>
       </c>
       <c r="G40" s="1">
-        <v>7867</v>
+        <f>'[1]לוח 1 table'!$M39</f>
+        <v>8328</v>
       </c>
       <c r="H40" s="1">
-        <v>7256</v>
+        <f>'[1]לוח 1 table'!$L39</f>
+        <v>7539</v>
       </c>
       <c r="I40" s="1">
-        <v>7588</v>
+        <f>'[1]לוח 1 table'!$K39</f>
+        <v>7656</v>
       </c>
       <c r="J40" s="1">
-        <v>3046</v>
+        <f>'[1]לוח 1 table'!$I39</f>
+        <v>3216</v>
       </c>
       <c r="K40" s="1">
-        <v>2845.0301307505601</v>
+        <f>'[1]לוח 1 table'!$H39</f>
+        <v>2912</v>
       </c>
       <c r="L40" s="1">
-        <v>2988</v>
+        <f>'[1]לוח 1 table'!$G39</f>
+        <v>2948</v>
       </c>
       <c r="M40" s="1">
-        <v>4821</v>
+        <f>'[1]לוח 1 table'!$D39</f>
+        <v>5112</v>
       </c>
       <c r="N40" s="1">
-        <v>4411</v>
+        <f>'[1]לוח 1 table'!$C39</f>
+        <v>4627</v>
       </c>
       <c r="O40" s="1">
-        <v>4712</v>
-      </c>
-      <c r="P40" s="1">
-        <v>78623</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>78972</v>
-      </c>
-      <c r="R40" s="1">
-        <v>77848</v>
-      </c>
-      <c r="S40" s="1">
-        <v>671</v>
-      </c>
-      <c r="T40">
-        <v>207</v>
-      </c>
-      <c r="U40">
-        <v>464</v>
-      </c>
-      <c r="V40" s="1">
-        <v>932</v>
-      </c>
-      <c r="W40">
-        <v>432</v>
-      </c>
-      <c r="X40">
-        <v>500</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>1133</v>
-      </c>
-      <c r="Z40">
-        <v>285</v>
-      </c>
-      <c r="AA40">
-        <v>848</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>1935</v>
-      </c>
-      <c r="AC40">
-        <v>759</v>
-      </c>
-      <c r="AD40">
-        <v>1176</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>1344</v>
-      </c>
-      <c r="AF40">
-        <v>613</v>
-      </c>
-      <c r="AG40">
-        <v>731</v>
-      </c>
-      <c r="AH40" s="1">
-        <v>1558</v>
-      </c>
-      <c r="AI40">
-        <v>606</v>
-      </c>
-      <c r="AJ40">
-        <v>952</v>
-      </c>
-      <c r="AK40" s="1">
-        <v>196</v>
-      </c>
-      <c r="AL40">
+        <f>'[1]לוח 1 table'!$B39</f>
+        <v>4826</v>
+      </c>
+      <c r="P40" s="7">
+        <f>'[2]2'!$E35</f>
+        <v>78534</v>
+      </c>
+      <c r="Q40" s="7">
+        <f>'[2]2'!$D35</f>
+        <v>79054</v>
+      </c>
+      <c r="R40" s="7">
+        <f>'[2]2'!$C35</f>
+        <v>78590</v>
+      </c>
+      <c r="S40" s="7">
+        <f t="shared" si="0"/>
+        <v>732</v>
+      </c>
+      <c r="T40" s="8">
+        <f>'[3]לוח 3 table'!$G50</f>
+        <v>230</v>
+      </c>
+      <c r="U40" s="8">
+        <f>'[3]לוח 3 table'!$G104</f>
+        <v>502</v>
+      </c>
+      <c r="V40" s="7">
+        <f t="shared" si="1"/>
+        <v>943</v>
+      </c>
+      <c r="W40" s="8">
+        <f>'[3]לוח 3 table'!$F50</f>
+        <v>408</v>
+      </c>
+      <c r="X40" s="8">
+        <f>'[3]לוח 3 table'!$F104</f>
+        <v>535</v>
+      </c>
+      <c r="Y40" s="7">
+        <f t="shared" si="2"/>
+        <v>1193</v>
+      </c>
+      <c r="Z40" s="8">
+        <f>'[3]לוח 3 table'!$E50</f>
+        <v>334</v>
+      </c>
+      <c r="AA40" s="8">
+        <f>'[3]לוח 3 table'!$E104</f>
+        <v>859</v>
+      </c>
+      <c r="AB40" s="7">
+        <f t="shared" si="3"/>
+        <v>2107</v>
+      </c>
+      <c r="AC40" s="8">
+        <f>'[3]לוח 3 table'!$D50</f>
+        <v>877</v>
+      </c>
+      <c r="AD40" s="8">
+        <f>'[3]לוח 3 table'!$D104</f>
+        <v>1230</v>
+      </c>
+      <c r="AE40" s="7">
+        <f t="shared" si="4"/>
+        <v>1444</v>
+      </c>
+      <c r="AF40" s="8">
+        <f>'[3]לוח 3 table'!$C50</f>
+        <v>653</v>
+      </c>
+      <c r="AG40" s="8">
+        <f>'[3]לוח 3 table'!$C104</f>
+        <v>791</v>
+      </c>
+      <c r="AH40" s="7">
+        <f t="shared" si="5"/>
+        <v>1675</v>
+      </c>
+      <c r="AI40" s="8">
+        <f>'[3]לוח 3 table'!$B50</f>
+        <v>642</v>
+      </c>
+      <c r="AJ40" s="8">
+        <f>'[3]לוח 3 table'!$B104</f>
+        <v>1033</v>
+      </c>
+      <c r="AK40" s="7">
+        <f t="shared" si="6"/>
+        <v>206</v>
+      </c>
+      <c r="AL40" s="8">
+        <f>'[3]לוח 3 table'!$A50</f>
         <v>45</v>
       </c>
-      <c r="AM40">
-        <v>151</v>
+      <c r="AM40" s="8">
+        <f>'[3]לוח 3 table'!$A104</f>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41">
+        <v>2025</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="G41" s="1">
+        <f>'[1]לוח 1 table'!$M40</f>
+        <v>6282</v>
+      </c>
+      <c r="H41" s="1">
+        <f>'[1]לוח 1 table'!$L40</f>
+        <v>7242</v>
+      </c>
+      <c r="I41" s="1">
+        <f>'[1]לוח 1 table'!$K40</f>
+        <v>7521</v>
+      </c>
+      <c r="J41" s="1">
+        <f>'[1]לוח 1 table'!$I40</f>
+        <v>2353</v>
+      </c>
+      <c r="K41" s="1">
+        <f>'[1]לוח 1 table'!$H40</f>
+        <v>2734</v>
+      </c>
+      <c r="L41" s="1">
+        <f>'[1]לוח 1 table'!$G40</f>
+        <v>2865</v>
+      </c>
+      <c r="M41" s="1">
+        <f>'[1]לוח 1 table'!$D40</f>
+        <v>3929</v>
+      </c>
+      <c r="N41" s="1">
+        <f>'[1]לוח 1 table'!$C40</f>
+        <v>4507</v>
+      </c>
+      <c r="O41" s="1">
+        <f>'[1]לוח 1 table'!$B40</f>
+        <v>4681</v>
+      </c>
+      <c r="P41" s="7">
+        <f>'[2]2'!$E36</f>
+        <v>79408</v>
+      </c>
+      <c r="Q41" s="7">
+        <f>'[2]2'!$D36</f>
+        <v>80346</v>
+      </c>
+      <c r="R41" s="7">
+        <f>'[2]2'!$C36</f>
+        <v>79596</v>
+      </c>
+      <c r="S41" s="7">
+        <f t="shared" si="0"/>
+        <v>477</v>
+      </c>
+      <c r="T41" s="8">
+        <f>'[3]לוח 3 table'!$G51</f>
+        <v>159</v>
+      </c>
+      <c r="U41" s="8">
+        <f>'[3]לוח 3 table'!$G105</f>
+        <v>318</v>
+      </c>
+      <c r="V41" s="7">
+        <f t="shared" si="1"/>
+        <v>648</v>
+      </c>
+      <c r="W41" s="8">
+        <f>'[3]לוח 3 table'!$F51</f>
+        <v>212</v>
+      </c>
+      <c r="X41" s="8">
+        <f>'[3]לוח 3 table'!$F105</f>
+        <v>436</v>
+      </c>
+      <c r="Y41" s="7">
+        <f t="shared" si="2"/>
+        <v>869</v>
+      </c>
+      <c r="Z41" s="8">
+        <f>'[3]לוח 3 table'!$E51</f>
+        <v>172</v>
+      </c>
+      <c r="AA41" s="8">
+        <f>'[3]לוח 3 table'!$E105</f>
+        <v>697</v>
+      </c>
+      <c r="AB41" s="7">
+        <f t="shared" si="3"/>
+        <v>1629</v>
+      </c>
+      <c r="AC41" s="8">
+        <f>'[3]לוח 3 table'!$D51</f>
+        <v>701</v>
+      </c>
+      <c r="AD41" s="8">
+        <f>'[3]לוח 3 table'!$D105</f>
+        <v>928</v>
+      </c>
+      <c r="AE41" s="7">
+        <f t="shared" si="4"/>
+        <v>971</v>
+      </c>
+      <c r="AF41" s="8">
+        <f>'[3]לוח 3 table'!$C51</f>
+        <v>327</v>
+      </c>
+      <c r="AG41" s="8">
+        <f>'[3]לוח 3 table'!$C105</f>
+        <v>644</v>
+      </c>
+      <c r="AH41" s="7">
+        <f t="shared" si="5"/>
+        <v>1531</v>
+      </c>
+      <c r="AI41" s="8">
+        <f>'[3]לוח 3 table'!$B51</f>
+        <v>739</v>
+      </c>
+      <c r="AJ41" s="8">
+        <f>'[3]לוח 3 table'!$B105</f>
+        <v>792</v>
+      </c>
+      <c r="AK41" s="7">
+        <f t="shared" si="6"/>
+        <v>137</v>
+      </c>
+      <c r="AL41" s="8">
+        <f>'[3]לוח 3 table'!$A51</f>
+        <v>25</v>
+      </c>
+      <c r="AM41" s="8">
+        <f>'[3]לוח 3 table'!$A105</f>
+        <v>112</v>
+      </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
